--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>449.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.9%</t>
+          <t>-690.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.4%</t>
+          <t>-299.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-156.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-296.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.1%</t>
+          <t>-201.2%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.79583044472831</v>
+        <v>-9.961034686983604</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7647852183293571</v>
+        <v>-0.8308669152314749</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.619541802009406</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.58217830267007</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.088750821223472</v>
+        <v>-9.253955063478767</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4847404025877231</v>
+        <v>-0.550822099489841</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.619541802009406</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.57939126900977</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.048566522857282</v>
+        <v>-9.213770765112576</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4683230593534056</v>
+        <v>-0.5344047562555234</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.579357503643215</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.603845471917326</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.968496727319478</v>
+        <v>-9.133700969574772</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4369283199175271</v>
+        <v>-0.5030100168196445</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.499287708105411</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.651254170460765</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.73501550508988</v>
+        <v>-8.900219747345172</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3356114021878356</v>
+        <v>-0.4016930990899525</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.265806485875813</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.799267332636376</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.585349114082366</v>
+        <v>-8.750553356337658</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2786370560977889</v>
+        <v>-0.3447187529999058</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-2.172902994633277</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>1.852117217068939</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.453073640451478</v>
+        <v>-8.618277882706771</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2303593798984069</v>
+        <v>-0.2964410768005239</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-2.040627521002391</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>1.926849987994498</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.262473965778325</v>
+        <v>-8.427678208033617</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.151304449341509</v>
+        <v>-0.217386146243626</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.850027846329238</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.044024853486026</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.013474167094744</v>
+        <v>-8.178678409350036</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03879818864441775</v>
+        <v>-0.1048798855465347</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.850027846329238</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.056931194709684</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.119064156867848</v>
+        <v>-8.284268399123141</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2090101141528784</v>
+        <v>-0.2750918110549954</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.955617836102342</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>1.865601271246603</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.137799058986445</v>
+        <v>-8.303003301241738</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1679597331232308</v>
+        <v>-0.2340414300253477</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.961213845762473</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>1.910788007327611</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.989859017578846</v>
+        <v>-8.155063259834138</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2286626392483586</v>
+        <v>-0.2947443361504756</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.940892929853916</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.803101634184578</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.972700867447552</v>
+        <v>-8.137905109702844</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.230513365449319</v>
+        <v>-0.296595062351436</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.804682538009876</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.929152460676861</v>
+        <v>-8.094356702932153</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.220054614836136</v>
+        <v>-0.2861363117382525</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.797721925914783</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.687004067223003</v>
+        <v>-7.852208309478295</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1087329030734496</v>
+        <v>-0.1748145999755661</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.812184280295926</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.578744930100481</v>
+        <v>-7.743949172355773</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.07089712776524593</v>
+        <v>-0.1369788246673624</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.806716400755121</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.455453795283351</v>
+        <v>-7.620658037538642</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02408257982781681</v>
+        <v>-0.09016427672993332</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.800443644905491</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>1.878189175655977</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.434304596379907</v>
+        <v>-7.599508838635199</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.007921922029114015</v>
+        <v>-0.07400361893123097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.779294446002048</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>1.898579673235368</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.190539154396463</v>
+        <v>-7.355743396651754</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08536496311131403</v>
+        <v>0.01928326620919751</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.779294446002048</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>1.894360381582418</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.088776334119168</v>
+        <v>-7.25398057637446</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1281944051422483</v>
+        <v>0.06211270824013138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>1.904416136537892</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.838925940170093</v>
+        <v>-7.004130182425385</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.22087663770558</v>
+        <v>0.1547949408034635</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>1.897158211521594</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.66303384770266</v>
+        <v>-6.828238089957953</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2948325982132021</v>
+        <v>0.2287509013110851</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>1.900757335042242</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.491587384680197</v>
+        <v>-6.656791626935489</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3767386894767411</v>
+        <v>0.3106569925746241</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.594628914587156</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.016952718910274</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.266554385011374</v>
+        <v>-6.431758627266666</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4657723669605671</v>
+        <v>0.3996906700584502</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.369595914918333</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.150992996327865</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.20291864277744</v>
+        <v>-6.368122885032732</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4959214649084585</v>
+        <v>0.4298397680063415</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.305960172684399</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.193869242722543</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.159156461471598</v>
+        <v>-6.324360703726891</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4946205962145904</v>
+        <v>0.4285388993124735</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.305960172684399</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.175063501506338</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.918725964666738</v>
+        <v>-6.08393020692203</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5925358715614122</v>
+        <v>0.5264541746592952</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-1.065529675879538</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.321064876214132</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.846483396495543</v>
+        <v>-6.011687638750836</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6253622126647103</v>
+        <v>0.5592805157625933</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-1.065529675879538</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.324994190048952</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.793485074214155</v>
+        <v>-5.958689316469448</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6472401254946054</v>
+        <v>0.5811584285924885</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-1.010193416877599</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.358874529367455</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.684680188734428</v>
+        <v>-5.849884430989721</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6877601509064899</v>
+        <v>0.6216784540043729</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-1.010193416877599</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.355872600587449</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.464659390697418</v>
+        <v>-5.62986363295271</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7773475071319083</v>
+        <v>0.7112658102297913</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.8689735718096192</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.442183544638851</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.33179170163414</v>
+        <v>-5.496995943889432</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8463887655590425</v>
+        <v>0.7803070686569256</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.8689735718096192</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.458077727440675</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.17227659811477</v>
+        <v>-5.337480840370063</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9113406514070923</v>
+        <v>0.8452589545049753</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.7094584682902493</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.554932633992598</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.027604453015033</v>
+        <v>-5.192808695270325</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9792976120084269</v>
+        <v>0.91321591510631</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.5647863231905119</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.651824023613881</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.087479280372725</v>
+        <v>-5.252683522628018</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9413851724667759</v>
+        <v>0.8753034755646589</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.624661150548204</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.601936618600691</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.000679782593716</v>
+        <v>-5.165884024849008</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9985054649009457</v>
+        <v>0.932423767998829</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.624661150548204</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.624337111923257</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.003149489055522</v>
+        <v>-5.168353731310814</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9975899836896356</v>
+        <v>0.9315082867875186</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.6271308570100103</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.622927689419586</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.071519675379532</v>
+        <v>-5.236723917634825</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9812488316347334</v>
+        <v>0.9151671347326165</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.639500031316017</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.180057856295666</v>
+        <v>-5.345262098550958</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9282702679001713</v>
+        <v>0.8621885709980543</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.629936739947908</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.211051015624371</v>
+        <v>-5.376255257879664</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7405825692090757</v>
+        <v>0.6745008723069588</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.454646304988295</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.035576755831903</v>
+        <v>-5.200780998087195</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8153395051178509</v>
+        <v>0.749257808215734</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.459213536980083</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.146513008473152</v>
+        <v>-5.311717250728444</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7467070328225587</v>
+        <v>0.6806253359204417</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.43495556574129</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.349539586016385</v>
+        <v>-5.514743828271677</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6686277870251707</v>
+        <v>0.6025460901230537</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.316271004435255</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.191613987081092</v>
+        <v>-5.356818229336384</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7419704130314204</v>
+        <v>0.6758887161293035</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.326443390867388</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.105370524054714</v>
+        <v>-5.270574766310006</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7714140688158317</v>
+        <v>0.7053323719137148</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.321389661441248</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.150677343453694</v>
+        <v>-5.315881585708986</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7450671165007656</v>
+        <v>0.6789854195986487</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.8616918985262595</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.288679339080235</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.179710448155995</v>
+        <v>-5.344914690411287</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7340057476529465</v>
+        <v>0.6679240507508295</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.8616918985262595</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.289231212113337</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.086899966705135</v>
+        <v>-5.252104208960428</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7004026321246561</v>
+        <v>0.6343209352225392</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.7688814170754001</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.274190192875218</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.131289436034563</v>
+        <v>-5.296493678289855</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6845203203174859</v>
+        <v>0.6184386234153689</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.8132708864048278</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.249429987202162</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.018618217798313</v>
+        <v>-5.183822460053605</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7246645161237089</v>
+        <v>0.6585828192215919</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.7005996681685775</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.312108426655635</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.90624121661564</v>
+        <v>-5.071445458870932</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7751066124274453</v>
+        <v>0.7090249155253283</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.7005996681685775</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.317599722486302</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.104475785502371</v>
+        <v>-5.269680027757663</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7073099866412922</v>
+        <v>0.6412282897391752</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.8988342370553082</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.210156182922803</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.18747706652765</v>
+        <v>-5.352681308782942</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5124651942318339</v>
+        <v>0.4463834973297169</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.037369372207152</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.296091144970981</v>
+        <v>-5.461295387226273</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5891692235737072</v>
+        <v>0.5230875266715902</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.157519032926358</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.382689727952084</v>
+        <v>-5.547893970207376</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5690428164835888</v>
+        <v>0.5029611195814718</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.172032059028681</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.344306065393932</v>
+        <v>-5.509510307649225</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.581815722849218</v>
+        <v>0.515734025947101</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.8790214590243307</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.19248169790594</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.167189735358766</v>
+        <v>-5.332393977614059</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6493912837085865</v>
+        <v>0.5833095868064695</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.8790214590243307</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.189210726751242</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.212281980192312</v>
+        <v>-5.377486222447605</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6320377775370809</v>
+        <v>0.5659560806349639</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7757132599384265</v>
+        <v>-0.9409175021937205</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.251879037964698</v>
+        <v>2.152756492611521</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.032906558953544</v>
+        <v>-5.198110801208837</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6975749213390023</v>
+        <v>0.6314932244368854</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6189365017677079</v>
+        <v>-0.7841407440230018</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339732068173543</v>
+        <v>2.240609522820367</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.077920772474151</v>
+        <v>-5.243125014729443</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6603766912623494</v>
+        <v>0.5942949943602325</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6492853970823125</v>
+        <v>-0.8144896393376064</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.30233018631637</v>
+        <v>2.203207640963194</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.344925282746586</v>
+        <v>-5.510129525001878</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5592664494923212</v>
+        <v>0.4931847525902042</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-1.008852677380555</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.09228138047637</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.446123064183759</v>
+        <v>-5.611327306439051</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5179912588139537</v>
+        <v>0.4519095619118367</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.077261490925874</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.05044001424568</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.413647478012987</v>
+        <v>-5.578851720268279</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5285814548365795</v>
+        <v>0.4624997579344625</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.077261490925874</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.048039975799997</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.394609350305689</v>
+        <v>-5.559813592560982</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5327214251277432</v>
+        <v>0.4666397282256263</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.135445102257069</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>2.009654528209525</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.425735981456308</v>
+        <v>-5.5909402237116</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6978526416061763</v>
+        <v>0.6317709447040594</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.135445102257069</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.187236397148206</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.478056362057099</v>
+        <v>-5.643260604312392</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.677757818351993</v>
+        <v>0.611676121449876</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.100498242248197</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.209037842139662</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.498313660586057</v>
+        <v>-5.66351790284135</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.675663429337336</v>
+        <v>0.6095817324352191</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.100498242248197</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.215046372536588</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.350570690351055</v>
+        <v>-5.515774932606347</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8139132652233587</v>
+        <v>0.7478315683212418</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9326908850133134</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.39488343466954</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.452585372882276</v>
+        <v>-5.617789615137569</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7759010137423514</v>
+        <v>0.7098193168402345</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9326908850133134</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.397677056201021</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.315976028788183</v>
+        <v>-5.481180271043476</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.831207099771647</v>
+        <v>0.76512540286953</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6308772986639271</v>
+        <v>-0.796081540919221</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.579427556402312</v>
+        <v>2.480305011049135</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.458741361610834</v>
+        <v>-5.623945603866126</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7731814433826969</v>
+        <v>0.7070997464805799</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9388468737418714</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.492848833448832</v>
+        <v>2.393726288095655</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.396443362834711</v>
+        <v>-5.561647605090004</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.864436196689967</v>
+        <v>0.79835449978785</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9388468737418714</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.559184387245653</v>
+        <v>2.460061841892476</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.194653165169553</v>
+        <v>-5.359857407424846</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6537331481454278</v>
+        <v>0.5876514512433109</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.575624439317423</v>
+        <v>-0.740828681572717</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.386576174936543</v>
+        <v>2.287453629583367</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.13476248352696</v>
+        <v>-5.299966725782252</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7479796531246405</v>
+        <v>0.6818979562225236</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5157337576748295</v>
+        <v>-0.6809379999301235</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.492800816244275</v>
+        <v>2.393678270891098</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.232503028151934</v>
+        <v>-5.397707270407227</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7235111713906943</v>
+        <v>0.6574294744885774</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5316230358078098</v>
+        <v>-0.6968272780631037</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.49789498548053</v>
+        <v>2.398772440127353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.408840788274864</v>
+        <v>-5.574045030530156</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6515120481661945</v>
+        <v>0.5854303512640775</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.8731650381860332</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.390628310231444</v>
+        <v>2.291505764878267</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.408151416113641</v>
+        <v>-5.573355658368933</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6502794150706124</v>
+        <v>0.5841977181684954</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.8731650381860332</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.389119928271373</v>
+        <v>2.289997382918196</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.414722381168233</v>
+        <v>-5.579926623423526</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6475138964842113</v>
+        <v>0.5814321995820944</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.8797360032406261</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.385040216674053</v>
+        <v>2.285917671320877</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.406768410873461</v>
+        <v>-5.571972653128753</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.65069548460212</v>
+        <v>0.5846137877000031</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.8797360032406261</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.385040216674053</v>
+        <v>2.285917671320877</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.396395034540374</v>
+        <v>-5.561599276795667</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6612265921631595</v>
+        <v>0.5951448952610425</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7041583846522448</v>
+        <v>-0.8693626269075387</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.39764599950171</v>
+        <v>2.298523454148533</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.268710724746078</v>
+        <v>-5.43391496700137</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7171926894556031</v>
+        <v>0.6511109925534861</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5764740748579483</v>
+        <v>-0.7416783171132423</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.479148958753013</v>
+        <v>2.380026413399836</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.329377315148466</v>
+        <v>-5.494581557403759</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6796807257705195</v>
+        <v>0.6135990288684026</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.658172391576482</v>
+        <v>-0.823376633831776</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.416884641197765</v>
+        <v>2.317762095844588</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.264383455214821</v>
+        <v>-5.429587697470113</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7097759723546067</v>
+        <v>0.6436942754524897</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6313417769723266</v>
+        <v>-0.7965460192276206</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.437080712570887</v>
+        <v>2.33795816721771</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.365142090971819</v>
+        <v>-5.530346333227111</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6736334576828851</v>
+        <v>0.6075517607807681</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7201673456993321</v>
+        <v>-0.885371587954626</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.387946310965761</v>
+        <v>2.288823765612585</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.320939253885919</v>
+        <v>-5.486143496141211</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6971941950450824</v>
+        <v>0.6311124981429654</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6759645086134316</v>
+        <v>-0.8411687508687256</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.420347615745139</v>
+        <v>2.321225070391962</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.357918281549361</v>
+        <v>-5.523122523804654</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6808125844489532</v>
+        <v>0.6147308875468362</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.804194849077395</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.440941957289184</v>
+        <v>2.341819411936008</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.377976360414202</v>
+        <v>-5.543180602669494</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7240371180860565</v>
+        <v>0.6579554211839396</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.804194849077395</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.492189722472224</v>
+        <v>2.393067177119048</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.338045687236312</v>
+        <v>-5.503249929491604</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7384500919514658</v>
+        <v>0.6723683950493489</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5990599336442107</v>
+        <v>-0.7642641758995047</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.514588830973212</v>
+        <v>2.415466285620035</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.297575339673607</v>
+        <v>-5.462779581928899</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7495864592148176</v>
+        <v>0.6835047623127006</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5585895860815058</v>
+        <v>-0.7237938283367997</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.533819267749104</v>
+        <v>2.434696722395928</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.232351158546401</v>
+        <v>-5.397555400801694</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7928635357584048</v>
+        <v>0.7267818388562879</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.6585696472095941</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590141180518133</v>
+        <v>2.491018635164957</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.852893538994466</v>
+        <v>3.481325097929825</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.283116084564889</v>
+        <v>-5.28984425424586</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7685185376502899</v>
+        <v>0.7658272697779016</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.5380182333900625</v>
+        <v>-0.7227224547361021</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.559310455755956</v>
+        <v>2.448487922948332</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.5%</t>
+          <t>453.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.6%</t>
+          <t>-680.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.6%</t>
+          <t>-295.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.2%</t>
+          <t>-157.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-296.3%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.2%</t>
+          <t>-190.1%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.000150918729592</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.08543853296720005</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.163730796913976</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.1524655641859529</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.460392138724174</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.267351124980824</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.757902275471551</v>
+        <v>-8.66542331949849</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3903814842141777</v>
+        <v>-0.3533899018249538</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.140903664214182</v>
+        <v>-9.048424708241122</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5436841410328146</v>
+        <v>-0.5066925586435902</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.322773455199217</v>
+        <v>-9.230294499226156</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6138605414553981</v>
+        <v>-0.5768689590661737</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.682303777703218</v>
+        <v>-9.589824821730158</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7523223671589485</v>
+        <v>-0.7153307847697246</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.73265284115744</v>
+        <v>-9.64017388518438</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.76454597258346</v>
+        <v>-0.7275543901942356</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.830272118578836</v>
+        <v>-9.737793162605776</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8005519329302495</v>
+        <v>-0.7635603505410251</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.977798206584479</v>
+        <v>-9.885319250611419</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8566688118109345</v>
+        <v>-0.8196772294217101</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.18205638191434</v>
+        <v>-10.08957742594128</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9328588848242374</v>
+        <v>-0.895867302435013</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.32386615612113</v>
+        <v>-10.23138720014807</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9851002400225171</v>
+        <v>-0.9481086576332927</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.25039632445368</v>
+        <v>-10.15791736848062</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.940340605862116</v>
+        <v>-0.9033490234728916</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.42552074184023</v>
+        <v>-10.33304178586716</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9958351520692164</v>
+        <v>-0.958843569679992</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.65997283585472</v>
+        <v>-10.56749387988165</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.096835154576608</v>
+        <v>-1.059843572187384</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.94777668039195</v>
+        <v>-10.85529772441889</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.21862888316548</v>
+        <v>-1.181637300776256</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.00056283599228</v>
+        <v>-10.90808388001922</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.238627555567055</v>
+        <v>-1.20163597317783</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.12659962936057</v>
+        <v>-11.03412067338751</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.286348544285256</v>
+        <v>-1.249356961896031</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.07458411539176</v>
+        <v>-10.9821051594187</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.261552003011329</v>
+        <v>-1.224560420622105</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.21625595711588</v>
+        <v>-11.12377700114282</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.319695966599719</v>
+        <v>-1.282704384210495</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.16666511269104</v>
+        <v>-11.07418615671798</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.284806218664913</v>
+        <v>-1.247814636275689</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.15385771968627</v>
+        <v>-11.06137876371321</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.292734395109686</v>
+        <v>-1.255742812720463</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.92801256696686</v>
+        <v>-10.8355336109938</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.192817260985713</v>
+        <v>-1.155825678596489</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.80343391062926</v>
+        <v>-10.7109549546562</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.141846653894617</v>
+        <v>-1.104855071505393</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.85632919867355</v>
+        <v>-10.76385024270049</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.160370994950225</v>
+        <v>-1.123379412561</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.78419602338567</v>
+        <v>-10.69171706741261</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.125784020596435</v>
+        <v>-1.088792438207212</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.71282963077602</v>
+        <v>-10.62035067480296</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.106974725946442</v>
+        <v>-1.069983143557217</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.44899276357195</v>
+        <v>-10.35651380759889</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.011323460377721</v>
+        <v>-0.9743318779884969</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.18175096270356</v>
+        <v>-10.08927200673049</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9062613005297364</v>
+        <v>-0.869269718140512</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.08384392402706</v>
+        <v>-9.991364968054004</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8673988000326003</v>
+        <v>-0.8304072176433763</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.05989038305111</v>
+        <v>-9.967411427078046</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8571488774967242</v>
+        <v>-0.8201572951074998</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.961034686983604</v>
+        <v>-9.703351488755249</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8308669152314749</v>
+        <v>-0.7277936359401331</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.619541802009406</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.58217830267007</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.253955063478767</v>
+        <v>-8.996271865250412</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.550822099489841</v>
+        <v>-0.4477488201984992</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.619541802009406</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.57939126900977</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.213770765112576</v>
+        <v>-8.956087566884221</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5344047562555234</v>
+        <v>-0.4313314769641816</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.579357503643215</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.603845471917326</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.133700969574772</v>
+        <v>-8.876017771346417</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5030100168196445</v>
+        <v>-0.3999367375283027</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.499287708105411</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.651254170460765</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.900219747345172</v>
+        <v>-8.642536549116819</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4016930990899525</v>
+        <v>-0.2986198197986112</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.265806485875813</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.799267332636376</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.750553356337658</v>
+        <v>-8.492870158109305</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3447187529999058</v>
+        <v>-0.2416454737085649</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.172902994633277</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.852117217068939</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.618277882706771</v>
+        <v>-8.360594684478418</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2964410768005239</v>
+        <v>-0.193367797509183</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.040627521002391</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.926849987994498</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.427678208033617</v>
+        <v>-8.169995009805264</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.217386146243626</v>
+        <v>-0.1143128669522846</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.850027846329238</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.044024853486026</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.178678409350036</v>
+        <v>-7.920995211121683</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1048798855465347</v>
+        <v>-0.001806606255193355</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.850027846329238</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.056931194709684</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.284268399123141</v>
+        <v>-8.026585200894788</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2750918110549954</v>
+        <v>-0.172018531763654</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.955617836102342</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.865601271246603</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.303003301241738</v>
+        <v>-8.045320103013385</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2340414300253477</v>
+        <v>-0.1309681507340064</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.961213845762473</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.910788007327611</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.155063259834138</v>
+        <v>-7.897380061605785</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2947443361504756</v>
+        <v>-0.1916710568591342</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.940892929853916</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.803101634184578</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.137905109702844</v>
+        <v>-7.880221911474491</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.296595062351436</v>
+        <v>-0.1935217830600946</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.804682538009876</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.094356702932153</v>
+        <v>-7.836673504703801</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2861363117382525</v>
+        <v>-0.1830630324469116</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.797721925914783</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.852208309478295</v>
+        <v>-7.594525111249943</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1748145999755661</v>
+        <v>-0.07174132068422523</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.812184280295926</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.743949172355773</v>
+        <v>-7.486265974127421</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1369788246673624</v>
+        <v>-0.03390554537602153</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.806716400755121</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.620658037538642</v>
+        <v>-7.36297483931029</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09016427672993332</v>
+        <v>0.01290900256140759</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.800443644905491</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.878189175655977</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.599508838635199</v>
+        <v>-7.341825640406847</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.07400361893123097</v>
+        <v>0.02906966036010994</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.779294446002048</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.898579673235368</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.355743396651754</v>
+        <v>-7.098060198423402</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.01928326620919751</v>
+        <v>0.1223565455005384</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.779294446002048</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.894360381582418</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.25398057637446</v>
+        <v>-6.996297378146108</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.06211270824013138</v>
+        <v>0.1651859875314723</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.904416136537892</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.004130182425385</v>
+        <v>-6.746446984197033</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1547949408034635</v>
+        <v>0.2578682200948044</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.897158211521594</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.828238089957953</v>
+        <v>-6.5705548917296</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2287509013110851</v>
+        <v>0.3318241806024265</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.900757335042242</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.656791626935489</v>
+        <v>-6.399108428707136</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3106569925746241</v>
+        <v>0.4137302718659654</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.594628914587156</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.016952718910274</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.431758627266666</v>
+        <v>-6.174075429038314</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3996906700584502</v>
+        <v>0.5027639493497915</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.369595914918333</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.150992996327865</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.368122885032732</v>
+        <v>-6.110439686804379</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4298397680063415</v>
+        <v>0.5329130472976824</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.305960172684399</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.193869242722543</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.324360703726891</v>
+        <v>-6.066677505498538</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4285388993124735</v>
+        <v>0.5316121786038148</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.305960172684399</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.175063501506338</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.08393020692203</v>
+        <v>-5.826247008693677</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5264541746592952</v>
+        <v>0.6295274539506366</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.065529675879538</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.321064876214132</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.011687638750836</v>
+        <v>-5.754004440522483</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5592805157625933</v>
+        <v>0.6623537950539347</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.065529675879538</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.324994190048952</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.958689316469448</v>
+        <v>-5.701006118241095</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5811584285924885</v>
+        <v>0.6842317078838298</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.010193416877599</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.358874529367455</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.849884430989721</v>
+        <v>-5.592201232761368</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6216784540043729</v>
+        <v>0.7247517332957139</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.010193416877599</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.355872600587449</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.62986363295271</v>
+        <v>-5.372180434724357</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7112658102297913</v>
+        <v>0.8143390895211322</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8689735718096192</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.442183544638851</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.496995943889432</v>
+        <v>-5.23931274566108</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7803070686569256</v>
+        <v>0.8833803479482665</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8689735718096192</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.458077727440675</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.337480840370063</v>
+        <v>-5.07979764214171</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8452589545049753</v>
+        <v>0.9483322337963163</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7094584682902493</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.554932633992598</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.192808695270325</v>
+        <v>-4.935125497041972</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.91321591510631</v>
+        <v>1.016289194397651</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5647863231905119</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.651824023613881</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.252683522628018</v>
+        <v>-4.995000324399665</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8753034755646589</v>
+        <v>0.9783767548560003</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.624661150548204</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.601936618600691</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.165884024849008</v>
+        <v>-4.908200826620655</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.932423767998829</v>
+        <v>1.03549704729017</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.624661150548204</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.624337111923257</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.168353731310814</v>
+        <v>-4.910670533082461</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9315082867875186</v>
+        <v>1.03458156607886</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6271308570100103</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.622927689419586</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.236723917634825</v>
+        <v>-4.979040719406472</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9151671347326165</v>
+        <v>1.018240414023958</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.639500031316017</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.345262098550958</v>
+        <v>-5.087578900322606</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8621885709980543</v>
+        <v>0.9652618502893953</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.629936739947908</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.376255257879664</v>
+        <v>-5.118572059651311</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.6745008723069588</v>
+        <v>0.7775741515983001</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.454646304988295</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.200780998087195</v>
+        <v>-4.943097799858842</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.749257808215734</v>
+        <v>0.8523310875070753</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.459213536980083</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.311717250728444</v>
+        <v>-5.054034052500091</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6806253359204417</v>
+        <v>0.7836986152117826</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.43495556574129</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.514743828271677</v>
+        <v>-5.257060630043324</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6025460901230537</v>
+        <v>0.7056193694143951</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.316271004435255</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.356818229336384</v>
+        <v>-5.099135031108031</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6758887161293035</v>
+        <v>0.7789619954206448</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.326443390867388</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.270574766310006</v>
+        <v>-5.012891568081653</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7053323719137148</v>
+        <v>0.8084056512050561</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.321389661441248</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.315881585708986</v>
+        <v>-5.058198387480633</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6789854195986487</v>
+        <v>0.7820586988899896</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8616918985262595</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.288679339080235</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.344914690411287</v>
+        <v>-5.087231492182934</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6679240507508295</v>
+        <v>0.7709973300421709</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8616918985262595</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.289231212113337</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.252104208960428</v>
+        <v>-4.994421010732075</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6343209352225392</v>
+        <v>0.7373942145138803</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7688814170754001</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.274190192875218</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.296493678289855</v>
+        <v>-5.038810480061502</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6184386234153689</v>
+        <v>0.7215119027067103</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8132708864048278</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.249429987202162</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.183822460053605</v>
+        <v>-4.926139261825252</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6585828192215919</v>
+        <v>0.7616560985129333</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7005996681685775</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.312108426655635</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.071445458870932</v>
+        <v>-4.813762260642579</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7090249155253283</v>
+        <v>0.8120981948166697</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.7005996681685775</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.317599722486302</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.269680027757663</v>
+        <v>-5.01199682952931</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6412282897391752</v>
+        <v>0.7443015690305161</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8988342370553082</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.210156182922803</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.352681308782942</v>
+        <v>-5.094998110554589</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4463834973297169</v>
+        <v>0.5494567766210579</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.037369372207152</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.461295387226273</v>
+        <v>-5.20361218899792</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5230875266715902</v>
+        <v>0.6261608059629311</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.157519032926358</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.547893970207376</v>
+        <v>-5.290210771979023</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5029611195814718</v>
+        <v>0.6060343988728132</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.172032059028681</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.509510307649225</v>
+        <v>-5.251827109420872</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.515734025947101</v>
+        <v>0.618807305238442</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8790214590243307</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.19248169790594</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.332393977614059</v>
+        <v>-5.074710779385706</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5833095868064695</v>
+        <v>0.6863828660978104</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8790214590243307</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.189210726751242</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.377486222447605</v>
+        <v>-5.119803024219252</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5659560806349639</v>
+        <v>0.6690293599263053</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.9409175021937205</v>
+        <v>-0.7757132599384265</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.152756492611521</v>
+        <v>2.251879037964698</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.198110801208837</v>
+        <v>-4.940427602980484</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6314932244368854</v>
+        <v>0.7345665037282267</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.7841407440230018</v>
+        <v>-0.6189365017677079</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.240609522820367</v>
+        <v>2.339732068173543</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.243125014729443</v>
+        <v>-4.985441816501091</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5942949943602325</v>
+        <v>0.6973682736515738</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.8144896393376064</v>
+        <v>-0.6492853970823125</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.203207640963194</v>
+        <v>2.30233018631637</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.510129525001878</v>
+        <v>-5.252446326773526</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4931847525902042</v>
+        <v>0.5962580318815456</v>
       </c>
       <c r="F1959" t="n">
-        <v>-1.008852677380555</v>
+        <v>-0.8436484351252611</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.09228138047637</v>
+        <v>2.191403925829547</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.611327306439051</v>
+        <v>-5.353644108210698</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4519095619118367</v>
+        <v>0.5549828412031781</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.077261490925874</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.05044001424568</v>
+        <v>2.149562559598857</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.578851720268279</v>
+        <v>-5.321168522039926</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4624997579344625</v>
+        <v>0.5655730372258034</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.077261490925874</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.048039975799997</v>
+        <v>2.147162521153174</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.559813592560982</v>
+        <v>-5.302130394332629</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4666397282256263</v>
+        <v>0.5697130075169672</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.135445102257069</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.009654528209525</v>
+        <v>2.108777073562702</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.5909402237116</v>
+        <v>-5.333257025483247</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6317709447040594</v>
+        <v>0.7348442239954007</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.135445102257069</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.187236397148206</v>
+        <v>2.286358942501382</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.643260604312392</v>
+        <v>-5.385577406084039</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.611676121449876</v>
+        <v>0.7147494007412174</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.100498242248197</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.209037842139662</v>
+        <v>2.308160387492839</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.66351790284135</v>
+        <v>-5.405834704612997</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6095817324352191</v>
+        <v>0.71265501172656</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.100498242248197</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.215046372536588</v>
+        <v>2.314168917889765</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.515774932606347</v>
+        <v>-5.258091734377994</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7478315683212418</v>
+        <v>0.8509048476125831</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9326908850133134</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.39488343466954</v>
+        <v>2.494005980022717</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.617789615137569</v>
+        <v>-5.360106416909216</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7098193168402345</v>
+        <v>0.8128925961315754</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9326908850133134</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.397677056201021</v>
+        <v>2.496799601554198</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.481180271043476</v>
+        <v>-5.223497072815123</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.76512540286953</v>
+        <v>0.8681986821608709</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.796081540919221</v>
+        <v>-0.6308772986639271</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.480305011049135</v>
+        <v>2.579427556402312</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.623945603866126</v>
+        <v>-5.366262405637773</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7070997464805799</v>
+        <v>0.8101730257719213</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9388468737418714</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.393726288095655</v>
+        <v>2.492848833448832</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.561647605090004</v>
+        <v>-5.303964406861651</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.79835449978785</v>
+        <v>0.9014277790791909</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9388468737418714</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.460061841892476</v>
+        <v>2.559184387245653</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.359857407424846</v>
+        <v>-5.102174209196493</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5876514512433109</v>
+        <v>0.6907247305346522</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.740828681572717</v>
+        <v>-0.575624439317423</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.287453629583367</v>
+        <v>2.386576174936543</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.299966725782252</v>
+        <v>-5.0422835275539</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6818979562225236</v>
+        <v>0.7849712355138649</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6809379999301235</v>
+        <v>-0.5157337576748295</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.393678270891098</v>
+        <v>2.492800816244275</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.397707270407227</v>
+        <v>-5.140024072178874</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6574294744885774</v>
+        <v>0.7605027537799187</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6968272780631037</v>
+        <v>-0.5316230358078098</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.398772440127353</v>
+        <v>2.49789498548053</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.574045030530156</v>
+        <v>-5.316361832301803</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5854303512640775</v>
+        <v>0.6885036305554184</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8731650381860332</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.291505764878267</v>
+        <v>2.390628310231444</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.573355658368933</v>
+        <v>-5.31567246014058</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5841977181684954</v>
+        <v>0.6872709974598363</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8731650381860332</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.289997382918196</v>
+        <v>2.389119928271373</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.579926623423526</v>
+        <v>-5.322243425195173</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5814321995820944</v>
+        <v>0.6845054788734357</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8797360032406261</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.285917671320877</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.571972653128753</v>
+        <v>-5.314289454900401</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5846137877000031</v>
+        <v>0.6876870669913444</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8797360032406261</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.285917671320877</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.561599276795667</v>
+        <v>-5.303916078567314</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5951448952610425</v>
+        <v>0.6982181745523839</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8693626269075387</v>
+        <v>-0.7041583846522448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.298523454148533</v>
+        <v>2.39764599950171</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.43391496700137</v>
+        <v>-5.176231768773017</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6511109925534861</v>
+        <v>0.7541842718448271</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7416783171132423</v>
+        <v>-0.5764740748579483</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.380026413399836</v>
+        <v>2.479148958753013</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.494581557403759</v>
+        <v>-5.236898359175406</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6135990288684026</v>
+        <v>0.7166723081597439</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.823376633831776</v>
+        <v>-0.658172391576482</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.317762095844588</v>
+        <v>2.416884641197765</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.429587697470113</v>
+        <v>-5.17190449924176</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6436942754524897</v>
+        <v>0.7467675547438306</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7965460192276206</v>
+        <v>-0.6313417769723266</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.33795816721771</v>
+        <v>2.437080712570887</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.530346333227111</v>
+        <v>-5.272663134998758</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6075517607807681</v>
+        <v>0.7106250400721095</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.885371587954626</v>
+        <v>-0.7201673456993321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.288823765612585</v>
+        <v>2.387946310965761</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.486143496141211</v>
+        <v>-5.228460297912858</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6311124981429654</v>
+        <v>0.7341857774343068</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8411687508687256</v>
+        <v>-0.6759645086134316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.321225070391962</v>
+        <v>2.420347615745139</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.523122523804654</v>
+        <v>-5.265439325576301</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6147308875468362</v>
+        <v>0.7178041668381772</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.804194849077395</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.341819411936008</v>
+        <v>2.440941957289184</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.543180602669494</v>
+        <v>-5.285497404441141</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6579554211839396</v>
+        <v>0.7610287004752805</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.804194849077395</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.393067177119048</v>
+        <v>2.492189722472224</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.503249929491604</v>
+        <v>-5.245566731263251</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6723683950493489</v>
+        <v>0.7754416743406898</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7642641758995047</v>
+        <v>-0.5990599336442107</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.415466285620035</v>
+        <v>2.514588830973212</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.462779581928899</v>
+        <v>-5.205096383700546</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6835047623127006</v>
+        <v>0.786578041604042</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.7237938283367997</v>
+        <v>-0.5585895860815058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.434696722395928</v>
+        <v>2.533819267749104</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.397555400801694</v>
+        <v>-5.139872202573341</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7267818388562879</v>
+        <v>0.8298551181476288</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.6585696472095941</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.491018635164957</v>
+        <v>2.590141180518133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.481325097929825</v>
+        <v>3.834856610776928</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.28984425424586</v>
+        <v>-5.190366492930397</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7658272697779016</v>
+        <v>0.8056183743040868</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.7227224547361021</v>
+        <v>-0.5383861420803744</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.448487922948332</v>
+        <v>2.559089710541769</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.7%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.6%</t>
+          <t>-697.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.7%</t>
+          <t>-302.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-157.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-294.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.1%</t>
+          <t>-155.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1989"/>
+  <dimension ref="A1:G1990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.000150918729592</v>
+        <v>-8.00215066919284</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08543853296720005</v>
+        <v>-0.0862384331524999</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.163730796913976</v>
+        <v>-8.165730547377223</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1524655641859529</v>
+        <v>-0.1532654643712523</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.460392138724174</v>
+        <v>-8.462391889187421</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.267351124980824</v>
+        <v>-0.2681510251661234</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.66542331949849</v>
+        <v>-8.667423069961737</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3533899018249538</v>
+        <v>-0.3541898020102532</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.048424708241122</v>
+        <v>-9.050424458704368</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5066925586435902</v>
+        <v>-0.5074924588288896</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.230294499226156</v>
+        <v>-9.232294249689403</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5768689590661737</v>
+        <v>-0.5776688592514732</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.589824821730158</v>
+        <v>-9.591824572193405</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7153307847697246</v>
+        <v>-0.716130684955024</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.64017388518438</v>
+        <v>-9.642173635647627</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7275543901942356</v>
+        <v>-0.728354290379535</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.737793162605776</v>
+        <v>-9.739792913069023</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7635603505410251</v>
+        <v>-0.7643602507263245</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.885319250611419</v>
+        <v>-9.887319001074665</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8196772294217101</v>
+        <v>-0.8204771296070095</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.08957742594128</v>
+        <v>-10.09157717640453</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.895867302435013</v>
+        <v>-0.8966672026203124</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23138720014807</v>
+        <v>-10.23338695061132</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9481086576332927</v>
+        <v>-0.9489085578185921</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.15791736848062</v>
+        <v>-10.15991711894387</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9033490234728916</v>
+        <v>-0.904148923658191</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33304178586716</v>
+        <v>-10.33504153633041</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.958843569679992</v>
+        <v>-0.9596434698652914</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.56749387988165</v>
+        <v>-10.5694936303449</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.059843572187384</v>
+        <v>-1.060643472372683</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85529772441889</v>
+        <v>-10.85729747488214</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.181637300776256</v>
+        <v>-1.182437200961556</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.90808388001922</v>
+        <v>-10.91008363048247</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.20163597317783</v>
+        <v>-1.20243587336313</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03412067338751</v>
+        <v>-11.03612042385076</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.249356961896031</v>
+        <v>-1.250156862081331</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.9821051594187</v>
+        <v>-10.98410490988194</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.224560420622105</v>
+        <v>-1.225360320807405</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.12377700114282</v>
+        <v>-11.12577675160606</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.282704384210495</v>
+        <v>-1.283504284395795</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.07418615671798</v>
+        <v>-11.07618590718123</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.247814636275689</v>
+        <v>-1.248614536460988</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.06137876371321</v>
+        <v>-11.06337851417645</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.255742812720463</v>
+        <v>-1.256542712905762</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.8355336109938</v>
+        <v>-10.83753336145704</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.155825678596489</v>
+        <v>-1.156625578781788</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.7109549546562</v>
+        <v>-10.71295470511945</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.104855071505393</v>
+        <v>-1.105654971690692</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.76385024270049</v>
+        <v>-10.76584999316374</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.123379412561</v>
+        <v>-1.1241793127463</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69171706741261</v>
+        <v>-10.69371681787586</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.088792438207212</v>
+        <v>-1.089592338392511</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62035067480296</v>
+        <v>-10.62235042526621</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.069983143557217</v>
+        <v>-1.070783043742517</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.35651380759889</v>
+        <v>-10.35851355806214</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9743318779884969</v>
+        <v>-0.9751317781737963</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.08927200673049</v>
+        <v>-10.09127175719374</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.869269718140512</v>
+        <v>-0.8700696183258114</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.991364968054004</v>
+        <v>-9.993364718517251</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8304072176433763</v>
+        <v>-0.8312071178286757</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.967411427078046</v>
+        <v>-9.969411177541293</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8201572951074998</v>
+        <v>-0.8209571952927992</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.703351488755249</v>
+        <v>-9.87055548147379</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7277936359401331</v>
+        <v>-0.7946752330275499</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.619541802009406</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.58217830267007</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.996271865250412</v>
+        <v>-9.163475857968953</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4477488201984992</v>
+        <v>-0.514630417285916</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.619541802009406</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.57939126900977</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.956087566884221</v>
+        <v>-9.123291559602762</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4313314769641816</v>
+        <v>-0.4982130740515984</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.579357503643215</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.603845471917326</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.876017771346417</v>
+        <v>-9.043221764064958</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3999367375283027</v>
+        <v>-0.46681833461572</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.499287708105411</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.651254170460765</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.642536549116819</v>
+        <v>-8.809740541835358</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2986198197986112</v>
+        <v>-0.3655014168860276</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.265806485875813</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.799267332636376</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.492870158109305</v>
+        <v>-8.660074150827844</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2416454737085649</v>
+        <v>-0.3085270707959813</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-2.172902994633277</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>1.852117217068939</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.360594684478418</v>
+        <v>-8.527798677196957</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.193367797509183</v>
+        <v>-0.2602493945965993</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-2.040627521002391</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>1.926849987994498</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.169995009805264</v>
+        <v>-8.337199002523803</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1143128669522846</v>
+        <v>-0.181194464039701</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.850027846329238</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.044024853486026</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.920995211121683</v>
+        <v>-8.088199203840222</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.001806606255193355</v>
+        <v>-0.06868820334260972</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.850027846329238</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.056931194709684</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.026585200894788</v>
+        <v>-8.193789193613327</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.172018531763654</v>
+        <v>-0.2389001288510704</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.955617836102342</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>1.865601271246603</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.045320103013385</v>
+        <v>-8.212524095731924</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1309681507340064</v>
+        <v>-0.1978497478214227</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.961213845762473</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>1.910788007327611</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.897380061605785</v>
+        <v>-8.064584054324325</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1916710568591342</v>
+        <v>-0.2585526539465506</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.940892929853916</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.803101634184578</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.880221911474491</v>
+        <v>-8.04742590419303</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1935217830600946</v>
+        <v>-0.260403380147511</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.804682538009876</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.836673504703801</v>
+        <v>-8.003877497422341</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1830630324469116</v>
+        <v>-0.2499446295343279</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.797721925914783</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.594525111249943</v>
+        <v>-7.761729103968483</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.07174132068422523</v>
+        <v>-0.1386229177716416</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.812184280295926</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.486265974127421</v>
+        <v>-7.653469966845961</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03390554537602153</v>
+        <v>-0.1007871424634379</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.923734779722622</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.806716400755121</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.36297483931029</v>
+        <v>-7.53017883202883</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01290900256140759</v>
+        <v>-0.05397259452600878</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.800443644905491</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>1.878189175655977</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.341825640406847</v>
+        <v>-7.509029633125387</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02906966036010994</v>
+        <v>-0.03781193672730643</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.779294446002048</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>1.898579673235368</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.098060198423402</v>
+        <v>-7.265264191141942</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1223565455005384</v>
+        <v>0.05547494841312206</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.779294446002048</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>1.894360381582418</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.996297378146108</v>
+        <v>-7.163501370864648</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1651859875314723</v>
+        <v>0.09830439044405592</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>1.904416136537892</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.746446984197033</v>
+        <v>-6.913650976915573</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2578682200948044</v>
+        <v>0.190986623007388</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>1.897158211521594</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.5705548917296</v>
+        <v>-6.73775888444814</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3318241806024265</v>
+        <v>0.2649425835150101</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.766075377609619</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>1.900757335042242</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.399108428707136</v>
+        <v>-6.566312421425677</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4137302718659654</v>
+        <v>0.3468486747785491</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.594628914587156</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.016952718910274</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.174075429038314</v>
+        <v>-6.341279421756854</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5027639493497915</v>
+        <v>0.4358823522623752</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.369595914918333</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.150992996327865</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.110439686804379</v>
+        <v>-6.277643679522919</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5329130472976824</v>
+        <v>0.466031450210266</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.305960172684399</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.193869242722543</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.066677505498538</v>
+        <v>-6.233881498217078</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5316121786038148</v>
+        <v>0.4647305815163985</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.305960172684399</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.175063501506338</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.826247008693677</v>
+        <v>-5.993451001412217</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6295274539506366</v>
+        <v>0.5626458568632202</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-1.065529675879538</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.321064876214132</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.754004440522483</v>
+        <v>-5.921208433241023</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6623537950539347</v>
+        <v>0.5954721979665183</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-1.065529675879538</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.324994190048952</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.701006118241095</v>
+        <v>-5.868210110959635</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6842317078838298</v>
+        <v>0.6173501107964134</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-1.010193416877599</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.358874529367455</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.592201232761368</v>
+        <v>-5.759405225479908</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7247517332957139</v>
+        <v>0.6578701362082975</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-1.010193416877599</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.355872600587449</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.372180434724357</v>
+        <v>-5.539384427442897</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8143390895211322</v>
+        <v>0.7474574924337158</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.8689735718096192</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.442183544638851</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.23931274566108</v>
+        <v>-5.40651673837962</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8833803479482665</v>
+        <v>0.8164987508608501</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.8689735718096192</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.458077727440675</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.07979764214171</v>
+        <v>-5.24700163486025</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9483322337963163</v>
+        <v>0.8814506367088999</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.7094584682902493</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.554932633992598</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.935125497041972</v>
+        <v>-5.102329489760512</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.016289194397651</v>
+        <v>0.9494075973102349</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.5647863231905119</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.651824023613881</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.995000324399665</v>
+        <v>-5.162204317118205</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9783767548560003</v>
+        <v>0.9114951577685839</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.624661150548204</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.601936618600691</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.908200826620655</v>
+        <v>-5.075404819339195</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.03549704729017</v>
+        <v>0.9686154502027535</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.624661150548204</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.624337111923257</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.910670533082461</v>
+        <v>-5.077874525801001</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.03458156607886</v>
+        <v>0.9676999689914432</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.6271308570100103</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.622927689419586</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.979040719406472</v>
+        <v>-5.146244712125012</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.018240414023958</v>
+        <v>0.9513588169365415</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.639500031316017</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.087578900322606</v>
+        <v>-5.254782893041146</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9652618502893953</v>
+        <v>0.8983802532019789</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.629936739947908</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.118572059651311</v>
+        <v>-5.285776052369851</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7775741515983001</v>
+        <v>0.7106925545108838</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.454646304988295</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.943097799858842</v>
+        <v>-5.110301792577382</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8523310875070753</v>
+        <v>0.7854494904196589</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.459213536980083</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.054034052500091</v>
+        <v>-5.221238045218631</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7836986152117826</v>
+        <v>0.7168170181243663</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.6178551579737953</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.43495556574129</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.257060630043324</v>
+        <v>-5.424264622761864</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7056193694143951</v>
+        <v>0.6387377723269787</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.316271004435255</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.099135031108031</v>
+        <v>-5.266339023826571</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7789619954206448</v>
+        <v>0.7120803983332284</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.326443390867388</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.012891568081653</v>
+        <v>-5.180095560800194</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8084056512050561</v>
+        <v>0.7415240541176398</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.8208817355170287</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.321389661441248</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.058198387480633</v>
+        <v>-5.225402380199173</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7820586988899896</v>
+        <v>0.7151771018025732</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.8616918985262595</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.288679339080235</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.087231492182934</v>
+        <v>-5.254435484901474</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7709973300421709</v>
+        <v>0.7041157329547545</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.8616918985262595</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.289231212113337</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.994421010732075</v>
+        <v>-5.161625003450615</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7373942145138803</v>
+        <v>0.6705126174264637</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.7688814170754001</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.274190192875218</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.038810480061502</v>
+        <v>-5.206014472780042</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7215119027067103</v>
+        <v>0.6546303056192939</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.8132708864048278</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.249429987202162</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.926139261825252</v>
+        <v>-5.093343254543792</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7616560985129333</v>
+        <v>0.6947745014255169</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.7005996681685775</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.312108426655635</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.813762260642579</v>
+        <v>-4.980966253361119</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8120981948166697</v>
+        <v>0.7452165977292533</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.7005996681685775</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.317599722486302</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.01199682952931</v>
+        <v>-5.17920082224785</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7443015690305161</v>
+        <v>0.6774199719430998</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.8988342370553082</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.210156182922803</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.094998110554589</v>
+        <v>-5.262202103273129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5494567766210579</v>
+        <v>0.4825751795336415</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.037369372207152</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.20361218899792</v>
+        <v>-5.37081618171646</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6261608059629311</v>
+        <v>0.5592792088755147</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.157519032926358</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.290210771979023</v>
+        <v>-5.457414764697563</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6060343988728132</v>
+        <v>0.5391528017853968</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.9174051215824819</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.172032059028681</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.251827109420872</v>
+        <v>-5.419031102139412</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.618807305238442</v>
+        <v>0.5519257081510256</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.8790214590243307</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.19248169790594</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.074710779385706</v>
+        <v>-5.241914772104246</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6863828660978104</v>
+        <v>0.619501269010394</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.8790214590243307</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.189210726751242</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.119803024219252</v>
+        <v>-5.287007016937792</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6690293599263053</v>
+        <v>0.6021477628388889</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7757132599384265</v>
+        <v>-0.9409175021937205</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.251879037964698</v>
+        <v>2.152756492611521</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.940427602980484</v>
+        <v>-5.107631595699024</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7345665037282267</v>
+        <v>0.6676849066408104</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6189365017677079</v>
+        <v>-0.7841407440230018</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339732068173543</v>
+        <v>2.240609522820367</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.985441816501091</v>
+        <v>-5.152645809219631</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6973682736515738</v>
+        <v>0.6304866765641575</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6492853970823125</v>
+        <v>-0.8144896393376064</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.30233018631637</v>
+        <v>2.203207640963194</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.252446326773526</v>
+        <v>-5.419650319492066</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5962580318815456</v>
+        <v>0.5293764347941292</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-1.008852677380555</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.09228138047637</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.353644108210698</v>
+        <v>-5.520848100929238</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5549828412031781</v>
+        <v>0.4881012441157617</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.077261490925874</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.05044001424568</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.321168522039926</v>
+        <v>-5.488372514758466</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5655730372258034</v>
+        <v>0.4986914401383871</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.077261490925874</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.048039975799997</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.302130394332629</v>
+        <v>-5.469334387051169</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5697130075169672</v>
+        <v>0.5028314104295508</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.135445102257069</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>2.009654528209525</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.333257025483247</v>
+        <v>-5.500461018201787</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7348442239954007</v>
+        <v>0.6679626269079844</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.135445102257069</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.187236397148206</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.385577406084039</v>
+        <v>-5.552781398802579</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7147494007412174</v>
+        <v>0.647867803653801</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.100498242248197</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.209037842139662</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.405834704612997</v>
+        <v>-5.573038697331537</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.71265501172656</v>
+        <v>0.6457734146391436</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.100498242248197</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.215046372536588</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.258091734377994</v>
+        <v>-5.425295727096534</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8509048476125831</v>
+        <v>0.7840232505251667</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9326908850133134</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.39488343466954</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.360106416909216</v>
+        <v>-5.527310409627756</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8128925961315754</v>
+        <v>0.746010999044159</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9326908850133134</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.397677056201021</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.223497072815123</v>
+        <v>-5.390701065533663</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8681986821608709</v>
+        <v>0.8013170850734546</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6308772986639271</v>
+        <v>-0.796081540919221</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.579427556402312</v>
+        <v>2.480305011049135</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.366262405637773</v>
+        <v>-5.533466398356313</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8101730257719213</v>
+        <v>0.7432914286845049</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9388468737418714</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.492848833448832</v>
+        <v>2.393726288095655</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.303964406861651</v>
+        <v>-5.471168399580191</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9014277790791909</v>
+        <v>0.8345461819917745</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9388468737418714</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.559184387245653</v>
+        <v>2.460061841892476</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.102174209196493</v>
+        <v>-5.269378201915033</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6907247305346522</v>
+        <v>0.6238431334472359</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.575624439317423</v>
+        <v>-0.740828681572717</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.386576174936543</v>
+        <v>2.287453629583367</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.0422835275539</v>
+        <v>-5.20948752027244</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7849712355138649</v>
+        <v>0.7180896384264486</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5157337576748295</v>
+        <v>-0.6809379999301235</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.492800816244275</v>
+        <v>2.393678270891098</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.140024072178874</v>
+        <v>-5.307228064897414</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7605027537799187</v>
+        <v>0.6936211566925023</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5316230358078098</v>
+        <v>-0.6968272780631037</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.49789498548053</v>
+        <v>2.398772440127353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.316361832301803</v>
+        <v>-5.483565825020343</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6885036305554184</v>
+        <v>0.621622033468002</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.8731650381860332</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.390628310231444</v>
+        <v>2.291505764878267</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.31567246014058</v>
+        <v>-5.48287645285912</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6872709974598363</v>
+        <v>0.62038940037242</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.8731650381860332</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.389119928271373</v>
+        <v>2.289997382918196</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.322243425195173</v>
+        <v>-5.489447417913713</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6845054788734357</v>
+        <v>0.6176238817860193</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.8797360032406261</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.385040216674053</v>
+        <v>2.285917671320877</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.314289454900401</v>
+        <v>-5.481493447618941</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6876870669913444</v>
+        <v>0.620805469903928</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.8797360032406261</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.385040216674053</v>
+        <v>2.285917671320877</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.303916078567314</v>
+        <v>-5.471120071285854</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6982181745523839</v>
+        <v>0.6313365774649675</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7041583846522448</v>
+        <v>-0.8693626269075387</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.39764599950171</v>
+        <v>2.298523454148533</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.176231768773017</v>
+        <v>-5.343435761491557</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7541842718448271</v>
+        <v>0.6873026747574107</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5764740748579483</v>
+        <v>-0.7416783171132423</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.479148958753013</v>
+        <v>2.380026413399836</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.236898359175406</v>
+        <v>-5.404102351893946</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7166723081597439</v>
+        <v>0.6497907110723276</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.658172391576482</v>
+        <v>-0.823376633831776</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.416884641197765</v>
+        <v>2.317762095844588</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.17190449924176</v>
+        <v>-5.3391084919603</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7467675547438306</v>
+        <v>0.6798859576564142</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6313417769723266</v>
+        <v>-0.7965460192276206</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.437080712570887</v>
+        <v>2.33795816721771</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.272663134998758</v>
+        <v>-5.439867127717299</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7106250400721095</v>
+        <v>0.6437434429846931</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7201673456993321</v>
+        <v>-0.885371587954626</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.387946310965761</v>
+        <v>2.288823765612585</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.228460297912858</v>
+        <v>-5.395664290631398</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7341857774343068</v>
+        <v>0.6673041803468904</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6759645086134316</v>
+        <v>-0.8411687508687256</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.420347615745139</v>
+        <v>2.321225070391962</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.265439325576301</v>
+        <v>-5.432643318294841</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7178041668381772</v>
+        <v>0.6509225697507608</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.804194849077395</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.440941957289184</v>
+        <v>2.341819411936008</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.285497404441141</v>
+        <v>-5.452701397159681</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7610287004752805</v>
+        <v>0.6941471033878641</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.804194849077395</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.492189722472224</v>
+        <v>2.393067177119048</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.245566731263251</v>
+        <v>-5.412770723981791</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7754416743406898</v>
+        <v>0.7085600772532734</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5990599336442107</v>
+        <v>-0.7642641758995047</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.514588830973212</v>
+        <v>2.415466285620035</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.205096383700546</v>
+        <v>-5.372300376419086</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.786578041604042</v>
+        <v>0.7196964445166256</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5585895860815058</v>
+        <v>-0.7237938283367997</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.533819267749104</v>
+        <v>2.434696722395928</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.139872202573341</v>
+        <v>-5.307076195291881</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8298551181476288</v>
+        <v>0.7629735210602124</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.6585696472095941</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590141180518133</v>
+        <v>2.491018635164957</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,45 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.834856610776928</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.190366492930397</v>
+        <v>-5.357570485648937</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8056183743040868</v>
+        <v>0.7387367772166704</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.5383861420803744</v>
+        <v>-0.7035903843356683</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.559089710541769</v>
+        <v>2.459967165188592</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="2" t="n">
+        <v>45452</v>
+      </c>
+      <c r="B1990" t="n">
+        <v>3.834843566684785</v>
+      </c>
+      <c r="C1990" t="n">
+        <v>2.910753026664778</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>-5.357570485648937</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>0.7387367772166704</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>-0.7035903843356683</v>
+      </c>
+      <c r="G1990" t="n">
+        <v>2.903816823651145</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-697.3%</t>
+          <t>-686.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-302.3%</t>
+          <t>-298.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-156.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.4%</t>
+          <t>-274.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-156.2%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.00215066919284</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0862384331524999</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.165730547377223</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1532654643712523</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.462391889187421</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2681510251661234</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.667423069961737</v>
+        <v>-8.757902275471551</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3541898020102532</v>
+        <v>-0.3903814842141777</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.050424458704368</v>
+        <v>-9.140903664214182</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5074924588288896</v>
+        <v>-0.5436841410328146</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.232294249689403</v>
+        <v>-9.322773455199217</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5776688592514732</v>
+        <v>-0.6138605414553981</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.591824572193405</v>
+        <v>-9.682303777703218</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.716130684955024</v>
+        <v>-0.7523223671589485</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.642173635647627</v>
+        <v>-9.73265284115744</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.728354290379535</v>
+        <v>-0.76454597258346</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.739792913069023</v>
+        <v>-9.830272118578836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7643602507263245</v>
+        <v>-0.8005519329302495</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.887319001074665</v>
+        <v>-9.977798206584479</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8204771296070095</v>
+        <v>-0.8566688118109345</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.09157717640453</v>
+        <v>-10.18205638191434</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8966672026203124</v>
+        <v>-0.9328588848242374</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23338695061132</v>
+        <v>-10.32386615612113</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9489085578185921</v>
+        <v>-0.9851002400225171</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.15991711894387</v>
+        <v>-10.25039632445368</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.904148923658191</v>
+        <v>-0.940340605862116</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33504153633041</v>
+        <v>-10.42552074184023</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9596434698652914</v>
+        <v>-0.9958351520692164</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.5694936303449</v>
+        <v>-10.65997283585472</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.060643472372683</v>
+        <v>-1.096835154576608</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85729747488214</v>
+        <v>-10.94777668039195</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.182437200961556</v>
+        <v>-1.21862888316548</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.91008363048247</v>
+        <v>-11.00056283599228</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.20243587336313</v>
+        <v>-1.238627555567055</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03612042385076</v>
+        <v>-11.12659962936057</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.250156862081331</v>
+        <v>-1.286348544285256</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98410490988194</v>
+        <v>-11.07458411539176</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.225360320807405</v>
+        <v>-1.261552003011329</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.12577675160606</v>
+        <v>-11.21625595711588</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.283504284395795</v>
+        <v>-1.319695966599719</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.07618590718123</v>
+        <v>-11.16666511269104</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.248614536460988</v>
+        <v>-1.284806218664913</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.06337851417645</v>
+        <v>-11.15385771968627</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.256542712905762</v>
+        <v>-1.292734395109686</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.83753336145704</v>
+        <v>-10.92801256696686</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.156625578781788</v>
+        <v>-1.192817260985713</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.71295470511945</v>
+        <v>-10.80343391062926</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.105654971690692</v>
+        <v>-1.141846653894617</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.76584999316374</v>
+        <v>-10.85632919867355</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.1241793127463</v>
+        <v>-1.160370994950225</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69371681787586</v>
+        <v>-10.78419602338567</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.089592338392511</v>
+        <v>-1.125784020596435</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62235042526621</v>
+        <v>-10.71282963077602</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.070783043742517</v>
+        <v>-1.106974725946442</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.35851355806214</v>
+        <v>-10.44899276357195</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9751317781737963</v>
+        <v>-1.011323460377721</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09127175719374</v>
+        <v>-10.18175096270356</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8700696183258114</v>
+        <v>-0.9062613005297364</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.993364718517251</v>
+        <v>-10.08384392402706</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8312071178286757</v>
+        <v>-0.8673988000326003</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.969411177541293</v>
+        <v>-10.05989038305111</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8209571952927992</v>
+        <v>-0.8571488774967242</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.87055548147379</v>
+        <v>-9.79583044472831</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7946752330275499</v>
+        <v>-0.7647852183293571</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.619541802009406</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.58217830267007</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.163475857968953</v>
+        <v>-9.088750821223472</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.514630417285916</v>
+        <v>-0.4847404025877231</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.619541802009406</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.57939126900977</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.123291559602762</v>
+        <v>-9.048566522857282</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4982130740515984</v>
+        <v>-0.4683230593534056</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.579357503643215</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.603845471917326</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.043221764064958</v>
+        <v>-8.968496727319478</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.46681833461572</v>
+        <v>-0.4369283199175271</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.499287708105411</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.651254170460765</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.809740541835358</v>
+        <v>-8.73501550508988</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3655014168860276</v>
+        <v>-0.3356114021878356</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.265806485875813</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.799267332636376</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.660074150827844</v>
+        <v>-8.585349114082366</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3085270707959813</v>
+        <v>-0.2786370560977889</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.172902994633277</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.852117217068939</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.527798677196957</v>
+        <v>-8.453073640451478</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2602493945965993</v>
+        <v>-0.2303593798984069</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.040627521002391</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.926849987994498</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.337199002523803</v>
+        <v>-8.262473965778325</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.181194464039701</v>
+        <v>-0.151304449341509</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.850027846329238</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.044024853486026</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.088199203840222</v>
+        <v>-8.013474167094744</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.06868820334260972</v>
+        <v>-0.03879818864441775</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.850027846329238</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.056931194709684</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.193789193613327</v>
+        <v>-8.119064156867848</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2389001288510704</v>
+        <v>-0.2090101141528784</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.955617836102342</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.865601271246603</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.212524095731924</v>
+        <v>-8.137799058986445</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1978497478214227</v>
+        <v>-0.1679597331232308</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.961213845762473</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.910788007327611</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.064584054324325</v>
+        <v>-7.989859017578846</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2585526539465506</v>
+        <v>-0.2286626392483586</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.940892929853916</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.803101634184578</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.04742590419303</v>
+        <v>-7.972700867447552</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.260403380147511</v>
+        <v>-0.230513365449319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.804682538009876</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.003877497422341</v>
+        <v>-7.929152460676861</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2499446295343279</v>
+        <v>-0.220054614836136</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.797721925914783</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.761729103968483</v>
+        <v>-7.687004067223003</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1386229177716416</v>
+        <v>-0.1087329030734496</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.812184280295926</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.653469966845961</v>
+        <v>-7.578744930100481</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1007871424634379</v>
+        <v>-0.07089712776524593</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.923734779722622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.806716400755121</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.53017883202883</v>
+        <v>-7.455453795283351</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05397259452600878</v>
+        <v>-0.02408257982781681</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.800443644905491</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.878189175655977</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.509029633125387</v>
+        <v>-7.434304596379907</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03781193672730643</v>
+        <v>-0.007921922029114015</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.779294446002048</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.898579673235368</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.265264191141942</v>
+        <v>-7.190539154396463</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05547494841312206</v>
+        <v>0.08536496311131403</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.779294446002048</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.894360381582418</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.163501370864648</v>
+        <v>-7.088776334119168</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09830439044405592</v>
+        <v>0.1281944051422483</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.904416136537892</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.913650976915573</v>
+        <v>-6.838925940170093</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.190986623007388</v>
+        <v>0.22087663770558</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.897158211521594</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.73775888444814</v>
+        <v>-6.66303384770266</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2649425835150101</v>
+        <v>0.2948325982132021</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.766075377609619</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.900757335042242</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.566312421425677</v>
+        <v>-6.491587384680197</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3468486747785491</v>
+        <v>0.3767386894767411</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.594628914587156</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.016952718910274</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.341279421756854</v>
+        <v>-6.266554385011374</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4358823522623752</v>
+        <v>0.4657723669605671</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.369595914918333</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.150992996327865</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.277643679522919</v>
+        <v>-6.20291864277744</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.466031450210266</v>
+        <v>0.4959214649084585</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.305960172684399</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.193869242722543</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.233881498217078</v>
+        <v>-6.159156461471598</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4647305815163985</v>
+        <v>0.4946205962145904</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.305960172684399</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.175063501506338</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.993451001412217</v>
+        <v>-5.918725964666738</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5626458568632202</v>
+        <v>0.5925358715614122</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.065529675879538</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.321064876214132</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.921208433241023</v>
+        <v>-5.846483396495543</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5954721979665183</v>
+        <v>0.6253622126647103</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.065529675879538</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.324994190048952</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.868210110959635</v>
+        <v>-5.761418953695673</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6173501107964134</v>
+        <v>0.6600665737019984</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.010193416877599</v>
+        <v>-0.8148252570494496</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.358874529367455</v>
+        <v>2.476095425264345</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.759405225479908</v>
+        <v>-5.652614068215946</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6578701362082975</v>
+        <v>0.7005865991138829</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.010193416877599</v>
+        <v>-0.8148252570494496</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.355872600587449</v>
+        <v>2.473093496484339</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.539384427442897</v>
+        <v>-5.432593270178935</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7474574924337158</v>
+        <v>0.7901739553393012</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8689735718096192</v>
+        <v>-0.6736054119814694</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.442183544638851</v>
+        <v>2.559404440535741</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.40651673837962</v>
+        <v>-5.299725581115657</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8164987508608501</v>
+        <v>0.8592152137664355</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8689735718096192</v>
+        <v>-0.6736054119814694</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.458077727440675</v>
+        <v>2.575298623337564</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.24700163486025</v>
+        <v>-5.140210477596288</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8814506367088999</v>
+        <v>0.9241670996144853</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7094584682902493</v>
+        <v>-0.5140903084620995</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.554932633992598</v>
+        <v>2.672153529889489</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.102329489760512</v>
+        <v>-4.99553833249655</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9494075973102349</v>
+        <v>0.9921240602158201</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5647863231905119</v>
+        <v>-0.3694181633623621</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.651824023613881</v>
+        <v>2.769044919510771</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.162204317118205</v>
+        <v>-5.055413159854242</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9114951577685839</v>
+        <v>0.9542116206741689</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.624661150548204</v>
+        <v>-0.4292929907200542</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.601936618600691</v>
+        <v>2.719157514497581</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.075404819339195</v>
+        <v>-4.968613662075233</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9686154502027535</v>
+        <v>1.011331913108339</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.624661150548204</v>
+        <v>-0.4292929907200542</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.624337111923257</v>
+        <v>2.741558007820147</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.077874525801001</v>
+        <v>-4.971083368537039</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9676999689914432</v>
+        <v>1.010416431897029</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6271308570100103</v>
+        <v>-0.4317626971818603</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.622927689419586</v>
+        <v>2.740148585316476</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.146244712125012</v>
+        <v>-5.03945355486105</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9513588169365415</v>
+        <v>0.9940752798421264</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4224869981456454</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.639500031316017</v>
+        <v>2.756720927212907</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.254782893041146</v>
+        <v>-5.147991735777183</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8983802532019789</v>
+        <v>0.9410967161075643</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4224869981456454</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.629936739947908</v>
+        <v>2.747157635844798</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.285776052369851</v>
+        <v>-5.178984895105889</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7106925545108838</v>
+        <v>0.7534090174164687</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4224869981456454</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.454646304988295</v>
+        <v>2.571867200885185</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.110301792577382</v>
+        <v>-5.00351063531342</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7854494904196589</v>
+        <v>0.8281659533252441</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4224869981456454</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.459213536980083</v>
+        <v>2.576434432876972</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.221238045218631</v>
+        <v>-5.114446887954669</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7168170181243663</v>
+        <v>0.7595334810299517</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6178551579737953</v>
+        <v>-0.4224869981456454</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.43495556574129</v>
+        <v>2.552176461638179</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.424264622761864</v>
+        <v>-5.317473465497902</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6387377723269787</v>
+        <v>0.6814542352325641</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6255135756888788</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.316271004435255</v>
+        <v>2.433491900332145</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.266339023826571</v>
+        <v>-5.159547866562609</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7120803983332284</v>
+        <v>0.7547968612388134</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6255135756888788</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.326443390867388</v>
+        <v>2.443664286764278</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.180095560800194</v>
+        <v>-5.073304403536231</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7415240541176398</v>
+        <v>0.7842405170232247</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8208817355170287</v>
+        <v>-0.6255135756888788</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.321389661441248</v>
+        <v>2.438610557338138</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.225402380199173</v>
+        <v>-5.118611222935211</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7151771018025732</v>
+        <v>0.7578935647081586</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8616918985262595</v>
+        <v>-0.6663237386981096</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.288679339080235</v>
+        <v>2.405900234977125</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.254435484901474</v>
+        <v>-5.147644327637512</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7041157329547545</v>
+        <v>0.7468321958603394</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8616918985262595</v>
+        <v>-0.6663237386981096</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.289231212113337</v>
+        <v>2.406452108010226</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.161625003450615</v>
+        <v>-5.054833846186653</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6705126174264637</v>
+        <v>0.7132290803320491</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7688814170754001</v>
+        <v>-0.5735132572472502</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.274190192875218</v>
+        <v>2.391411088772108</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.206014472780042</v>
+        <v>-5.09922331551608</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6546303056192939</v>
+        <v>0.6973467685248789</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8132708864048278</v>
+        <v>-0.6179027265766779</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.249429987202162</v>
+        <v>2.366650883099052</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.093343254543792</v>
+        <v>-4.98655209727983</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6947745014255169</v>
+        <v>0.7374909643311021</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7005996681685775</v>
+        <v>-0.5052315083404277</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.312108426655635</v>
+        <v>2.429329322552525</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.980966253361119</v>
+        <v>-4.874175096097157</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7452165977292533</v>
+        <v>0.7879330606348385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.7005996681685775</v>
+        <v>-0.5052315083404277</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.317599722486302</v>
+        <v>2.434820618383192</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.17920082224785</v>
+        <v>-5.072409664983888</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6774199719430998</v>
+        <v>0.7201364348486852</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8988342370553082</v>
+        <v>-0.7034660772271584</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.210156182922803</v>
+        <v>2.327377078819693</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.262202103273129</v>
+        <v>-5.155410946009167</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4825751795336415</v>
+        <v>0.5252916424392269</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7220369617543322</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.037369372207152</v>
+        <v>2.154590268104042</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.37081618171646</v>
+        <v>-5.264025024452498</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5592792088755147</v>
+        <v>0.6019956717811001</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7220369617543322</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.157519032926358</v>
+        <v>2.274739928823247</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.457414764697563</v>
+        <v>-5.350623607433601</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5391528017853968</v>
+        <v>0.5818692646909818</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.9174051215824819</v>
+        <v>-0.7220369617543322</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.172032059028681</v>
+        <v>2.28925295492557</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.419031102139412</v>
+        <v>-5.31223994487545</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5519257081510256</v>
+        <v>0.594642171056611</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8790214590243307</v>
+        <v>-0.683653299196181</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.19248169790594</v>
+        <v>2.30970259380283</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.241914772104246</v>
+        <v>-5.135123614840284</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.619501269010394</v>
+        <v>0.6622177319159794</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8790214590243307</v>
+        <v>-0.683653299196181</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.189210726751242</v>
+        <v>2.306431622648132</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.287007016937792</v>
+        <v>-5.180215859673829</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6021477628388889</v>
+        <v>0.6448642257444743</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.9409175021937205</v>
+        <v>-0.7455493423655708</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.152756492611521</v>
+        <v>2.269977388508411</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.107631595699024</v>
+        <v>-5.000840438435062</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6676849066408104</v>
+        <v>0.7104013695463955</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.7841407440230018</v>
+        <v>-0.5887725841948521</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.240609522820367</v>
+        <v>2.357830418717257</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.152645809219631</v>
+        <v>-5.045854651955668</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6304866765641575</v>
+        <v>0.6732031394697429</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.8144896393376064</v>
+        <v>-0.6191214795094567</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.203207640963194</v>
+        <v>2.320428536860084</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.419650319492066</v>
+        <v>-5.312859162228103</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5293764347941292</v>
+        <v>0.5720928976997146</v>
       </c>
       <c r="F1959" t="n">
-        <v>-1.008852677380555</v>
+        <v>-0.8134845175524054</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.09228138047637</v>
+        <v>2.20950227637326</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.520848100929238</v>
+        <v>-5.414056943665276</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4881012441157617</v>
+        <v>0.5308177070213467</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.077261490925874</v>
+        <v>-0.8818933310977245</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.05044001424568</v>
+        <v>2.16766091014257</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.488372514758466</v>
+        <v>-5.381581357494504</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4986914401383871</v>
+        <v>0.5414079030439725</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.077261490925874</v>
+        <v>-0.8818933310977245</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.048039975799997</v>
+        <v>2.165260871696887</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.469334387051169</v>
+        <v>-5.362543229787207</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5028314104295508</v>
+        <v>0.5455478733351362</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.135445102257069</v>
+        <v>-0.940076942428919</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.009654528209525</v>
+        <v>2.126875424106415</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.500461018201787</v>
+        <v>-5.393669860937825</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6679626269079844</v>
+        <v>0.7106790898135693</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.135445102257069</v>
+        <v>-0.940076942428919</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.187236397148206</v>
+        <v>2.304457293045096</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.552781398802579</v>
+        <v>-5.445990241538617</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.647867803653801</v>
+        <v>0.6905842665593864</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.100498242248197</v>
+        <v>-0.9051300824200469</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.209037842139662</v>
+        <v>2.326258738036552</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.573038697331537</v>
+        <v>-5.466247540067575</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6457734146391436</v>
+        <v>0.688489877544729</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.100498242248197</v>
+        <v>-0.9051300824200469</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.215046372536588</v>
+        <v>2.332267268433478</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.425295727096534</v>
+        <v>-5.318504569832572</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7840232505251667</v>
+        <v>0.8267397134307521</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9326908850133134</v>
+        <v>-0.7373227251851637</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.39488343466954</v>
+        <v>2.51210433056643</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.527310409627756</v>
+        <v>-5.420519252363794</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.746010999044159</v>
+        <v>0.7887274619497444</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9326908850133134</v>
+        <v>-0.7373227251851637</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.397677056201021</v>
+        <v>2.514897952097911</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.390701065533663</v>
+        <v>-5.283909908269701</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8013170850734546</v>
+        <v>0.84403354797904</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.796081540919221</v>
+        <v>-0.6007133810910713</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.480305011049135</v>
+        <v>2.597525906946025</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.533466398356313</v>
+        <v>-5.426675241092351</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7432914286845049</v>
+        <v>0.7860078915900899</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9388468737418714</v>
+        <v>-0.7434787139137217</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.393726288095655</v>
+        <v>2.510947183992545</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.471168399580191</v>
+        <v>-5.364377242316229</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8345461819917745</v>
+        <v>0.8772626448973599</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9388468737418714</v>
+        <v>-0.7434787139137217</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.460061841892476</v>
+        <v>2.577282737789366</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.269378201915033</v>
+        <v>-5.162587044651071</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6238431334472359</v>
+        <v>0.6665595963528212</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.740828681572717</v>
+        <v>-0.5454605217445673</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.287453629583367</v>
+        <v>2.404674525480257</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.20948752027244</v>
+        <v>-5.102696363008477</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7180896384264486</v>
+        <v>0.7608061013320335</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6809379999301235</v>
+        <v>-0.4855698401019738</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.393678270891098</v>
+        <v>2.510899166787988</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.307228064897414</v>
+        <v>-5.200436907633452</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6936211566925023</v>
+        <v>0.7363376195980873</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6968272780631037</v>
+        <v>-0.5014591182349539</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.398772440127353</v>
+        <v>2.515993336024243</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.483565825020343</v>
+        <v>-5.376774667756381</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.621622033468002</v>
+        <v>0.6643384963735874</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8731650381860332</v>
+        <v>-0.6777968783578834</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.291505764878267</v>
+        <v>2.408726660775157</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.48287645285912</v>
+        <v>-5.376085295595158</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.62038940037242</v>
+        <v>0.6631058632780054</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8731650381860332</v>
+        <v>-0.6777968783578834</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.289997382918196</v>
+        <v>2.407218278815086</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.489447417913713</v>
+        <v>-5.382656260649751</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6176238817860193</v>
+        <v>0.6603403446916043</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8797360032406261</v>
+        <v>-0.6843678434124764</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.285917671320877</v>
+        <v>2.403138567217766</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.481493447618941</v>
+        <v>-5.374702290354978</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.620805469903928</v>
+        <v>0.6635219328095134</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8797360032406261</v>
+        <v>-0.6843678434124764</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.285917671320877</v>
+        <v>2.403138567217766</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.471120071285854</v>
+        <v>-5.364328914021891</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6313365774649675</v>
+        <v>0.6740530403705525</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8693626269075387</v>
+        <v>-0.673994467079389</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.298523454148533</v>
+        <v>2.415744350045423</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.343435761491557</v>
+        <v>-5.236644604227595</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6873026747574107</v>
+        <v>0.7300191376629961</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7416783171132423</v>
+        <v>-0.5463101572850926</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.380026413399836</v>
+        <v>2.497247309296726</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.404102351893946</v>
+        <v>-5.297311194629984</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6497907110723276</v>
+        <v>0.6925071739779129</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.823376633831776</v>
+        <v>-0.6280084740036262</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.317762095844588</v>
+        <v>2.434982991741478</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.3391084919603</v>
+        <v>-5.232317334696338</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6798859576564142</v>
+        <v>0.7226024205619996</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7965460192276206</v>
+        <v>-0.6011778593994709</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.33795816721771</v>
+        <v>2.4551790631146</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.439867127717299</v>
+        <v>-5.333075970453336</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6437434429846931</v>
+        <v>0.6864599058902785</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.885371587954626</v>
+        <v>-0.6900034281264763</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.288823765612585</v>
+        <v>2.406044661509475</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.395664290631398</v>
+        <v>-5.288873133367436</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6673041803468904</v>
+        <v>0.7100206432524758</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8411687508687256</v>
+        <v>-0.6458005910405759</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.321225070391962</v>
+        <v>2.438445966288852</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.432643318294841</v>
+        <v>-5.325852161030879</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6509225697507608</v>
+        <v>0.6936390326563462</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.804194849077395</v>
+        <v>-0.6088266892492453</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.341819411936008</v>
+        <v>2.459040307832898</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.452701397159681</v>
+        <v>-5.345910239895719</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6941471033878641</v>
+        <v>0.7368635662934495</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.804194849077395</v>
+        <v>-0.6088266892492453</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.393067177119048</v>
+        <v>2.510288073015938</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.412770723981791</v>
+        <v>-5.305979566717829</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7085600772532734</v>
+        <v>0.7512765401588588</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7642641758995047</v>
+        <v>-0.568896016071355</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.415466285620035</v>
+        <v>2.532687181516925</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.372300376419086</v>
+        <v>-5.265509219155124</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7196964445166256</v>
+        <v>0.7624129074222106</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.7237938283367997</v>
+        <v>-0.52842566850865</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.434696722395928</v>
+        <v>2.551917618292818</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.307076195291881</v>
+        <v>-5.200285038027919</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7629735210602124</v>
+        <v>0.8056899839657978</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.6585696472095941</v>
+        <v>-0.4632014873814444</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.491018635164957</v>
+        <v>2.608239531061846</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.357570485648937</v>
+        <v>-5.250779328384975</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7387367772166704</v>
+        <v>0.7814532401222558</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.7035903843356683</v>
+        <v>-0.5082222245075186</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.459967165188592</v>
+        <v>2.577188061085482</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.834843566684785</v>
+        <v>3.844641517518305</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.910753026664778</v>
+        <v>2.905033727793834</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.357570485648937</v>
+        <v>-5.250779328384975</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7387367772166704</v>
+        <v>0.7814532401222558</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.7035903843356683</v>
+        <v>-0.5082222245075186</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.903816823651145</v>
+        <v>2.898097524780201</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-31.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.7%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.7%</t>
+          <t>-689.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.1%</t>
+          <t>-299.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-154.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-274.8%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.2%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.102696363008477</v>
+        <v>-5.132543559495525</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7608061013320335</v>
+        <v>0.7488672227372146</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4855698401019738</v>
+        <v>-0.5154170365890213</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.510899166787988</v>
+        <v>2.49299084889576</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.200436907633452</v>
+        <v>-5.230284104120499</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7363376195980873</v>
+        <v>0.7243987410032684</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5014591182349539</v>
+        <v>-0.5313063147220015</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.515993336024243</v>
+        <v>2.498085018132015</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.376774667756381</v>
+        <v>-5.406621864243428</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6643384963735874</v>
+        <v>0.6523996177787685</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6777968783578834</v>
+        <v>-0.707644074844931</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.408726660775157</v>
+        <v>2.390818342882929</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.376085295595158</v>
+        <v>-5.405932492082205</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6631058632780054</v>
+        <v>0.6511669846831865</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6777968783578834</v>
+        <v>-0.707644074844931</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.407218278815086</v>
+        <v>2.389309960922858</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.382656260649751</v>
+        <v>-5.412503457136798</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6603403446916043</v>
+        <v>0.6484014660967854</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6843678434124764</v>
+        <v>-0.7142150398995238</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.403138567217766</v>
+        <v>2.385230249325538</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.374702290354978</v>
+        <v>-5.404549486842026</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6635219328095134</v>
+        <v>0.6515830542146945</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6843678434124764</v>
+        <v>-0.7142150398995238</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.403138567217766</v>
+        <v>2.385230249325538</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.364328914021891</v>
+        <v>-5.394176110508939</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6740530403705525</v>
+        <v>0.6621141617757336</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.673994467079389</v>
+        <v>-0.7038416635664365</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.415744350045423</v>
+        <v>2.397836032153195</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.236644604227595</v>
+        <v>-5.266491800714642</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7300191376629961</v>
+        <v>0.7180802590681772</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5463101572850926</v>
+        <v>-0.5761573537721401</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.497247309296726</v>
+        <v>2.479338991404498</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.297311194629984</v>
+        <v>-5.327158391117031</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6925071739779129</v>
+        <v>0.680568295383094</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6280084740036262</v>
+        <v>-0.6578556704906737</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.434982991741478</v>
+        <v>2.41707467384925</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.232317334696338</v>
+        <v>-5.262164531183386</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7226024205619996</v>
+        <v>0.7106635419671807</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6011778593994709</v>
+        <v>-0.6310250558865184</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.4551790631146</v>
+        <v>2.437270745222372</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.333075970453336</v>
+        <v>-5.362923166940384</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6864599058902785</v>
+        <v>0.6745210272954596</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6900034281264763</v>
+        <v>-0.7198506246135238</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.406044661509475</v>
+        <v>2.388136343617246</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.288873133367436</v>
+        <v>-5.318720329854483</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7100206432524758</v>
+        <v>0.6980817646576569</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6458005910405759</v>
+        <v>-0.6756477875276233</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.438445966288852</v>
+        <v>2.420537648396624</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.325852161030879</v>
+        <v>-5.355699357517926</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6936390326563462</v>
+        <v>0.6817001540615273</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6088266892492453</v>
+        <v>-0.6386738857362928</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.459040307832898</v>
+        <v>2.44113198994067</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.345910239895719</v>
+        <v>-5.375757436382766</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7368635662934495</v>
+        <v>0.7249246876986306</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6088266892492453</v>
+        <v>-0.6386738857362928</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.510288073015938</v>
+        <v>2.492379755123709</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.305979566717829</v>
+        <v>-5.335826763204876</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7512765401588588</v>
+        <v>0.7393376615640399</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.568896016071355</v>
+        <v>-0.5987432125584025</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.532687181516925</v>
+        <v>2.514778863624697</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232393</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.265509219155124</v>
+        <v>-5.295356415642171</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7624129074222106</v>
+        <v>0.7504740288273917</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.52842566850865</v>
+        <v>-0.5582728649956975</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.551917618292818</v>
+        <v>2.534009300400589</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162108</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.200285038027919</v>
+        <v>-5.230132234514966</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8056899839657978</v>
+        <v>0.7937511053709789</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4632014873814444</v>
+        <v>-0.4930486838684919</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.608239531061846</v>
+        <v>2.590331213169618</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.844630202204511</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.250779328384975</v>
+        <v>-5.280626524872022</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7814532401222558</v>
+        <v>0.7695143615274369</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.5082222245075186</v>
+        <v>-0.5380694209945661</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.577188061085482</v>
+        <v>2.559279743193254</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.844641517518305</v>
+        <v>3.761890380487964</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.905033727793834</v>
+        <v>2.799531195969919</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.250779328384975</v>
+        <v>-5.280626524872022</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7814532401222558</v>
+        <v>0.7695143615274369</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.5082222245075186</v>
+        <v>-0.5380694209945661</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.898097524780201</v>
+        <v>2.792594992956287</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.6%</t>
+          <t>-684.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.3%</t>
+          <t>-297.2%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-156.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-157.7%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.299543587314687</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.2067906803462374</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.596204929124886</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.3216762411411085</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.757902275471551</v>
+        <v>-8.801236109899202</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3903814842141777</v>
+        <v>-0.4077150179852382</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.140903664214182</v>
+        <v>-9.184237498641833</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5436841410328146</v>
+        <v>-0.5610176748038747</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.322773455199217</v>
+        <v>-9.366107289626868</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6138605414553981</v>
+        <v>-0.6311940752264587</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.682303777703218</v>
+        <v>-9.725637612130869</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7523223671589485</v>
+        <v>-0.769655900930009</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.73265284115744</v>
+        <v>-9.775986675585091</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.76454597258346</v>
+        <v>-0.7818795063545205</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.830272118578836</v>
+        <v>-9.873605953006487</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8005519329302495</v>
+        <v>-0.81788546670131</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.977798206584479</v>
+        <v>-10.02113204101213</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8566688118109345</v>
+        <v>-0.8740023455819945</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.18205638191434</v>
+        <v>-10.22539021634199</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9328588848242374</v>
+        <v>-0.9501924185952983</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.32386615612113</v>
+        <v>-10.36719999054878</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9851002400225171</v>
+        <v>-1.002433773793577</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.25039632445368</v>
+        <v>-10.29373015888133</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.940340605862116</v>
+        <v>-0.957674139633176</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.42552074184023</v>
+        <v>-10.46885457626788</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9958351520692164</v>
+        <v>-1.013168685840277</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.65997283585472</v>
+        <v>-10.70330667028237</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.096835154576608</v>
+        <v>-1.114168688347668</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.94777668039195</v>
+        <v>-10.9911105148196</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.21862888316548</v>
+        <v>-1.235962416936541</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.00056283599228</v>
+        <v>-11.04389667041993</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.238627555567055</v>
+        <v>-1.255961089338115</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.12659962936057</v>
+        <v>-11.16993346378822</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.286348544285256</v>
+        <v>-1.303682078056316</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.07458411539176</v>
+        <v>-11.11791794981941</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.261552003011329</v>
+        <v>-1.27888553678239</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.21625595711588</v>
+        <v>-11.25958979154353</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.319695966599719</v>
+        <v>-1.33702950037078</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.16666511269104</v>
+        <v>-11.20999894711869</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.284806218664913</v>
+        <v>-1.302139752435974</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.15385771968627</v>
+        <v>-11.19719155411392</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.292734395109686</v>
+        <v>-1.310067928880747</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.92801256696686</v>
+        <v>-10.97134640139451</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.192817260985713</v>
+        <v>-1.210150794756774</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.80343391062926</v>
+        <v>-10.84676774505692</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.141846653894617</v>
+        <v>-1.159180187665678</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.85632919867355</v>
+        <v>-10.8996630331012</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.160370994950225</v>
+        <v>-1.177704528721286</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.78419602338567</v>
+        <v>-10.82752985781332</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.125784020596435</v>
+        <v>-1.143117554367497</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.71282963077602</v>
+        <v>-10.75616346520368</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.106974725946442</v>
+        <v>-1.124308259717503</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.44899276357195</v>
+        <v>-10.49232659799961</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.011323460377721</v>
+        <v>-1.028656994148782</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.18175096270356</v>
+        <v>-10.22508479713121</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9062613005297364</v>
+        <v>-0.9235948343007974</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.08384392402706</v>
+        <v>-10.12717775845472</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8673988000326003</v>
+        <v>-0.8847323338036621</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.05989038305111</v>
+        <v>-10.10322421747876</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8571488774967242</v>
+        <v>-0.8744824112677851</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.79583044472831</v>
+        <v>-9.839164279155963</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7647852183293571</v>
+        <v>-0.7821187521004185</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.088750821223472</v>
+        <v>-9.132084655651125</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4847404025877231</v>
+        <v>-0.5020739363587845</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.048566522857282</v>
+        <v>-9.091900357284935</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4683230593534056</v>
+        <v>-0.485656593124467</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.968496727319478</v>
+        <v>-9.01183056174713</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4369283199175271</v>
+        <v>-0.4542618536885881</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.73501550508988</v>
+        <v>-8.778349339517533</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3356114021878356</v>
+        <v>-0.3529449359588965</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.585349114082366</v>
+        <v>-8.628682948510018</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2786370560977889</v>
+        <v>-0.2959705898688503</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.453073640451478</v>
+        <v>-8.496407474879131</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2303593798984069</v>
+        <v>-0.2476929136694683</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.262473965778325</v>
+        <v>-8.305807800205978</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.151304449341509</v>
+        <v>-0.1686379831125699</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.013474167094744</v>
+        <v>-8.056808001522397</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03879818864441775</v>
+        <v>-0.0561317224154787</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.119064156867848</v>
+        <v>-8.162397991295501</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2090101141528784</v>
+        <v>-0.2263436479239394</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.137799058986445</v>
+        <v>-8.181132893414098</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1679597331232308</v>
+        <v>-0.1852932668942917</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.989859017578846</v>
+        <v>-8.033192852006499</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2286626392483586</v>
+        <v>-0.2459961730194196</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.972700867447552</v>
+        <v>-8.016034701875205</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.230513365449319</v>
+        <v>-0.2478468992203799</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.929152460676861</v>
+        <v>-7.972486295104514</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.220054614836136</v>
+        <v>-0.2373881486071969</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.687004067223003</v>
+        <v>-7.730337901650656</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1087329030734496</v>
+        <v>-0.1260664368445106</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.578744930100481</v>
+        <v>-7.622078764528134</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.07089712776524593</v>
+        <v>-0.08823066153630688</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.455453795283351</v>
+        <v>-7.498787629711003</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02408257982781681</v>
+        <v>-0.04141611359887776</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.434304596379907</v>
+        <v>-7.47763843080756</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.007921922029114015</v>
+        <v>-0.02525545580017541</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.190539154396463</v>
+        <v>-7.233872988824116</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08536496311131403</v>
+        <v>0.06803142934025308</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.088776334119168</v>
+        <v>-7.132110168546821</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1281944051422483</v>
+        <v>0.1108608713711869</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.838925940170093</v>
+        <v>-6.882259774597746</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.22087663770558</v>
+        <v>0.203543103934519</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.66303384770266</v>
+        <v>-6.706367682130313</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2948325982132021</v>
+        <v>0.2774990644421411</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.491587384680197</v>
+        <v>-6.53492121910785</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3767386894767411</v>
+        <v>0.3594051557056801</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.266554385011374</v>
+        <v>-6.309888219439027</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4657723669605671</v>
+        <v>0.4484388331895062</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.20291864277744</v>
+        <v>-6.246252477205092</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4959214649084585</v>
+        <v>0.4785879311373971</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.159156461471598</v>
+        <v>-6.202490295899251</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4946205962145904</v>
+        <v>0.4772870624435295</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.918725964666738</v>
+        <v>-5.962059799094391</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5925358715614122</v>
+        <v>0.5752023377903512</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.846483396495543</v>
+        <v>-5.889817230923196</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6253622126647103</v>
+        <v>0.6080286788936493</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.761418953695673</v>
+        <v>-5.836818908641808</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6600665737019984</v>
+        <v>0.6299065917235445</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8148252570494496</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.476095425264345</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.652614068215946</v>
+        <v>-5.728014023162081</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7005865991138829</v>
+        <v>0.6704266171354285</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8148252570494496</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.473093496484339</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.432593270178935</v>
+        <v>-5.507993225125071</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7901739553393012</v>
+        <v>0.7600139733608469</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6736054119814694</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.559404440535741</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.299725581115657</v>
+        <v>-5.375125536061793</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8592152137664355</v>
+        <v>0.8290552317879811</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6736054119814694</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.575298623337564</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.140210477596288</v>
+        <v>-5.215610432542423</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9241670996144853</v>
+        <v>0.8940071176360309</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5140903084620995</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.672153529889489</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.99553833249655</v>
+        <v>-5.070938287442686</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9921240602158201</v>
+        <v>0.961964078237366</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3694181633623621</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.769044919510771</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.055413159854242</v>
+        <v>-5.130813114800378</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9542116206741689</v>
+        <v>0.9240516386957149</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4292929907200542</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.719157514497581</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.968613662075233</v>
+        <v>-5.044013617021369</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.011331913108339</v>
+        <v>0.9811719311298845</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4292929907200542</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.741558007820147</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.971083368537039</v>
+        <v>-5.046483323483175</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.010416431897029</v>
+        <v>0.9802564499185742</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4317626971818603</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.740148585316476</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.03945355486105</v>
+        <v>-5.114853509807185</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9940752798421264</v>
+        <v>0.9639152978636725</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4224869981456454</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.756720927212907</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.147991735777183</v>
+        <v>-5.223391690723319</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9410967161075643</v>
+        <v>0.9109367341291099</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4224869981456454</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.747157635844798</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.178984895105889</v>
+        <v>-5.254384850052024</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7534090174164687</v>
+        <v>0.7232490354380148</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4224869981456454</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.571867200885185</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.00351063531342</v>
+        <v>-5.078910590259555</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8281659533252441</v>
+        <v>0.79800597134679</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4224869981456454</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.576434432876972</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.114446887954669</v>
+        <v>-5.091490523822313</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7595334810299517</v>
+        <v>0.7687160266828941</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4224869981456454</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.552176461638179</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.317473465497902</v>
+        <v>-5.294517101365546</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6814542352325641</v>
+        <v>0.6906367808855065</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6255135756888788</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.433491900332145</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.159547866562609</v>
+        <v>-5.136591502430253</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7547968612388134</v>
+        <v>0.7639794068917558</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6255135756888788</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.443664286764278</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.073304403536231</v>
+        <v>-5.050348039403875</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7842405170232247</v>
+        <v>0.7934230626761671</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6255135756888788</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.438610557338138</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.118611222935211</v>
+        <v>-5.095654858802855</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7578935647081586</v>
+        <v>0.767076110361101</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6663237386981096</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.405900234977125</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.147644327637512</v>
+        <v>-5.124687963505156</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7468321958603394</v>
+        <v>0.7560147415132819</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6663237386981096</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.406452108010226</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.054833846186653</v>
+        <v>-5.031877482054297</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7132290803320491</v>
+        <v>0.7224116259849915</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5735132572472502</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.391411088772108</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.09922331551608</v>
+        <v>-5.076266951383724</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6973467685248789</v>
+        <v>0.7065293141778213</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6179027265766779</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.366650883099052</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.98655209727983</v>
+        <v>-4.963595733147474</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7374909643311021</v>
+        <v>0.7466735099840445</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5052315083404277</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.429329322552525</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.874175096097157</v>
+        <v>-4.851218731964801</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7879330606348385</v>
+        <v>0.7971156062877809</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5052315083404277</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.434820618383192</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.072409664983888</v>
+        <v>-5.049453300851532</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7201364348486852</v>
+        <v>0.7293189805016276</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7034660772271584</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.327377078819693</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.155410946009167</v>
+        <v>-5.132454581876811</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5252916424392269</v>
+        <v>0.5344741880921693</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7220369617543322</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.154590268104042</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.264025024452498</v>
+        <v>-5.241068660320142</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6019956717811001</v>
+        <v>0.6111782174340425</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7220369617543322</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.274739928823247</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.350623607433601</v>
+        <v>-5.327667243301245</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5818692646909818</v>
+        <v>0.5910518103439242</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7220369617543322</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.28925295492557</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.31223994487545</v>
+        <v>-5.289283580743094</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.594642171056611</v>
+        <v>0.6038247167095534</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.683653299196181</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.30970259380283</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.135123614840284</v>
+        <v>-5.112167250707928</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6622177319159794</v>
+        <v>0.6714002775689218</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.683653299196181</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.306431622648132</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.180215859673829</v>
+        <v>-5.157259495541473</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6448642257444743</v>
+        <v>0.6540467713974167</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7455493423655708</v>
+        <v>-0.7757132599384265</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.269977388508411</v>
+        <v>2.251879037964698</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.000840438435062</v>
+        <v>-4.977884074302706</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7104013695463955</v>
+        <v>0.719583915199338</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5887725841948521</v>
+        <v>-0.6189365017677079</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.357830418717257</v>
+        <v>2.339732068173543</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.045854651955668</v>
+        <v>-5.022898287823311</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6732031394697429</v>
+        <v>0.6823856851226853</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6191214795094567</v>
+        <v>-0.6492853970823125</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.320428536860084</v>
+        <v>2.30233018631637</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.312859162228103</v>
+        <v>-5.289902798095746</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5720928976997146</v>
+        <v>0.581275443352657</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8134845175524054</v>
+        <v>-0.8436484351252611</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.20950227637326</v>
+        <v>2.191403925829547</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.414056943665276</v>
+        <v>-5.391100579532919</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5308177070213467</v>
+        <v>0.5400002526742895</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8818933310977245</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.16766091014257</v>
+        <v>2.149562559598857</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.381581357494504</v>
+        <v>-5.358624993362147</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5414079030439725</v>
+        <v>0.5505904486969153</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8818933310977245</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.165260871696887</v>
+        <v>2.147162521153174</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.362543229787207</v>
+        <v>-5.33958686565485</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5455478733351362</v>
+        <v>0.5547304189880791</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.940076942428919</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.126875424106415</v>
+        <v>2.108777073562702</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.393669860937825</v>
+        <v>-5.370713496805468</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7106790898135693</v>
+        <v>0.7198616354665122</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.940076942428919</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.304457293045096</v>
+        <v>2.286358942501382</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.445990241538617</v>
+        <v>-5.42303387740626</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6905842665593864</v>
+        <v>0.6997668122123288</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9051300824200469</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.326258738036552</v>
+        <v>2.308160387492839</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.466247540067575</v>
+        <v>-5.443291175935218</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.688489877544729</v>
+        <v>0.6976724231976719</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9051300824200469</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.332267268433478</v>
+        <v>2.314168917889765</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.318504569832572</v>
+        <v>-5.295548205700215</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8267397134307521</v>
+        <v>0.8359222590836946</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7373227251851637</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.51210433056643</v>
+        <v>2.494005980022717</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.420519252363794</v>
+        <v>-5.397562888231437</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7887274619497444</v>
+        <v>0.7979100076026873</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7373227251851637</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.514897952097911</v>
+        <v>2.496799601554198</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.283909908269701</v>
+        <v>-5.260953544137344</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.84403354797904</v>
+        <v>0.8532160936319828</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6007133810910713</v>
+        <v>-0.6308772986639271</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.597525906946025</v>
+        <v>2.579427556402312</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.426675241092351</v>
+        <v>-5.403718876959994</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7860078915900899</v>
+        <v>0.7951904372430327</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7434787139137217</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.510947183992545</v>
+        <v>2.492848833448832</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.364377242316229</v>
+        <v>-5.341420878183872</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8772626448973599</v>
+        <v>0.8864451905503028</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7434787139137217</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.577282737789366</v>
+        <v>2.559184387245653</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.162587044651071</v>
+        <v>-5.139630680518714</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6665595963528212</v>
+        <v>0.6757421420057637</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5454605217445673</v>
+        <v>-0.575624439317423</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.404674525480257</v>
+        <v>2.386576174936543</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.132543559495525</v>
+        <v>-5.07973999887612</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7488672227372146</v>
+        <v>0.7699886469849764</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5154170365890213</v>
+        <v>-0.5157337576748295</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.49299084889576</v>
+        <v>2.492800816244275</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.230284104120499</v>
+        <v>-5.177480543501095</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7243987410032684</v>
+        <v>0.7455201652510302</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5313063147220015</v>
+        <v>-0.5316230358078098</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.498085018132015</v>
+        <v>2.49789498548053</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.406621864243428</v>
+        <v>-5.353818303624024</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6523996177787685</v>
+        <v>0.6735210420265303</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.707644074844931</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.390818342882929</v>
+        <v>2.390628310231444</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.405932492082205</v>
+        <v>-5.353128931462801</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6511669846831865</v>
+        <v>0.6722884089309482</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.707644074844931</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.389309960922858</v>
+        <v>2.389119928271373</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.412503457136798</v>
+        <v>-5.359699896517394</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6484014660967854</v>
+        <v>0.6695228903445472</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7142150398995238</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.385230249325538</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.404549486842026</v>
+        <v>-5.351745926222621</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6515830542146945</v>
+        <v>0.6727044784624558</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7142150398995238</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.385230249325538</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.394176110508939</v>
+        <v>-5.341372549889535</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6621141617757336</v>
+        <v>0.6832355860234953</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7038416635664365</v>
+        <v>-0.7041583846522448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.397836032153195</v>
+        <v>2.39764599950171</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.266491800714642</v>
+        <v>-5.213688240095238</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7180802590681772</v>
+        <v>0.7392016833159389</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5761573537721401</v>
+        <v>-0.5764740748579483</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.479338991404498</v>
+        <v>2.479148958753013</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.327158391117031</v>
+        <v>-5.274354830497627</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.680568295383094</v>
+        <v>0.7016897196308554</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6578556704906737</v>
+        <v>-0.658172391576482</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.41707467384925</v>
+        <v>2.416884641197765</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.262164531183386</v>
+        <v>-5.209360970563981</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7106635419671807</v>
+        <v>0.7317849662149425</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6310250558865184</v>
+        <v>-0.6313417769723266</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.437270745222372</v>
+        <v>2.437080712570887</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.362923166940384</v>
+        <v>-5.310119606320979</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6745210272954596</v>
+        <v>0.6956424515432209</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7198506246135238</v>
+        <v>-0.7201673456993321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.388136343617246</v>
+        <v>2.387946310965761</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.318720329854483</v>
+        <v>-5.265916769235079</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6980817646576569</v>
+        <v>0.7192031889054182</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6756477875276233</v>
+        <v>-0.6759645086134316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.420537648396624</v>
+        <v>2.420347615745139</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.355699357517926</v>
+        <v>-5.302895796898522</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6817001540615273</v>
+        <v>0.702821578309289</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6386738857362928</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.44113198994067</v>
+        <v>2.440941957289184</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.375757436382766</v>
+        <v>-5.322953875763362</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7249246876986306</v>
+        <v>0.7460461119463924</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6386738857362928</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.492379755123709</v>
+        <v>2.492189722472224</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078277</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.335826763204876</v>
+        <v>-5.283023202585472</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7393376615640399</v>
+        <v>0.7604590858118017</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5987432125584025</v>
+        <v>-0.5990599336442107</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.514778863624697</v>
+        <v>2.514588830973212</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232393</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.295356415642171</v>
+        <v>-5.242552855022767</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7504740288273917</v>
+        <v>0.7715954530751534</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5582728649956975</v>
+        <v>-0.5585895860815058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.534009300400589</v>
+        <v>2.533819267749104</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162108</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.230132234514966</v>
+        <v>-5.177328673895562</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7937511053709789</v>
+        <v>0.8148725296187407</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4930486838684919</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590331213169618</v>
+        <v>2.590141180518133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.844630202204511</v>
+        <v>3.494849985589694</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.280626524872022</v>
+        <v>-5.227822964252618</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7695143615274369</v>
+        <v>0.7906357857751987</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.5380694209945661</v>
+        <v>-0.5383861420803744</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.559279743193254</v>
+        <v>2.559089710541769</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.761890380487964</v>
+        <v>4.01743599277118</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.799531195969919</v>
+        <v>2.890144269074951</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.280626524872022</v>
+        <v>-5.227822964252618</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7695143615274369</v>
+        <v>0.7906357857751987</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.5380694209945661</v>
+        <v>-0.5383861420803744</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.792594992956287</v>
+        <v>2.883208066061319</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.4%</t>
+          <t>-707.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-297.2%</t>
+          <t>-306.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-268.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.7%</t>
+          <t>-184.2%</t>
         </is>
       </c>
     </row>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.299543587314687</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2067906803462374</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.596204929124886</v>
+        <v>-8.460765905223921</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3216762411411085</v>
+        <v>-0.2675006315807229</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.598833449148414</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.157862085333545</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.801236109899202</v>
+        <v>-8.665797085998237</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4077150179852382</v>
+        <v>-0.3535394084248527</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.598833449148414</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.153835780799142</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.184237498641833</v>
+        <v>-9.048798474740869</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5610176748038747</v>
+        <v>-0.5068420652434891</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.598833449148414</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.153733679477558</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.366107289626868</v>
+        <v>-9.230668265725903</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6311940752264587</v>
+        <v>-0.5770184656660726</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.780703240133449</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>2.047183320857967</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.725637612130869</v>
+        <v>-9.590198588229905</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.769655900930009</v>
+        <v>-0.715480291369623</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.780703240133449</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>2.052533624156017</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.775986675585091</v>
+        <v>-9.640547651684127</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7818795063545205</v>
+        <v>-0.7277038967941345</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.831052303587671</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>2.030240206040661</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.873605953006487</v>
+        <v>-9.738166929105523</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.81788546670131</v>
+        <v>-0.763709857140924</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-1.928671581009067</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.974710390209593</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02113204101213</v>
+        <v>-9.885693017111166</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8740023455819945</v>
+        <v>-0.8198267360216089</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.076197669014711</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.889088293727778</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22539021634199</v>
+        <v>-10.08995119244103</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9501924185952983</v>
+        <v>-0.8960168090349123</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.2038366136287</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.818018124078028</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36719999054878</v>
+        <v>-10.23176096664782</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.002433773793577</v>
+        <v>-0.9482581642331911</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.375115411274275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.719733399975118</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29373015888133</v>
+        <v>-10.15829113498037</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.957674139633176</v>
+        <v>-0.9034985300727909</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.301645579606827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.779187000469008</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.46885457626788</v>
+        <v>-10.33341555236691</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.013168685840277</v>
+        <v>-0.9589930762798913</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.476769996993371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.688667570784599</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70330667028237</v>
+        <v>-10.5678676463814</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.114168688347668</v>
+        <v>-1.059993078787283</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.476769996993371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.681448405883003</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.9911105148196</v>
+        <v>-10.85567149091864</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.235962416936541</v>
+        <v>-1.181786807376155</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.764573841530609</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.502093908386684</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04389667041993</v>
+        <v>-10.90845764651897</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.255961089338115</v>
+        <v>-1.201785479777729</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.860249328113006</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.445804406275802</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.16993346378822</v>
+        <v>-11.03449443988726</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.303682078056316</v>
+        <v>-1.24950646849593</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.834997705303263</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.463649108590762</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.11791794981941</v>
+        <v>-10.98247892591844</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.27888553678239</v>
+        <v>-1.224709927222004</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.834997705303263</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.467639444277163</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.25958979154353</v>
+        <v>-11.12415076764256</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.33702950037078</v>
+        <v>-1.282853890810394</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.834997705303263</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.466164217378421</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.20999894711869</v>
+        <v>-11.07455992321773</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.302139752435974</v>
+        <v>-1.247964142875588</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.785406860878429</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.510972134198194</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19719155411392</v>
+        <v>-11.06175253021295</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.310067928880747</v>
+        <v>-1.255892319320361</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.834262635887331</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.46860753554617</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97134640139451</v>
+        <v>-10.83590737749354</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.210150794756774</v>
+        <v>-1.155975185196388</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.792335960300167</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.503342613934677</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84676774505692</v>
+        <v>-10.71132872115595</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.159180187665678</v>
+        <v>-1.105004578105293</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.792335960300167</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.504481758490736</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.8996630331012</v>
+        <v>-10.76422400920024</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.177704528721286</v>
+        <v>-1.1235289191609</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.787380614211721</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.510088740305911</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.82752985781332</v>
+        <v>-10.69209083391236</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.143117554367497</v>
+        <v>-1.088941944807111</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.787380614211721</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.515822444544548</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75616346520368</v>
+        <v>-10.62072444130271</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.124308259717503</v>
+        <v>-1.070132650157117</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.716014221602073</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.548905017716471</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49232659799961</v>
+        <v>-10.35688757409864</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.028656994148782</v>
+        <v>-0.9744813845883971</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.716014221602073</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.539021536403564</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22508479713121</v>
+        <v>-10.08964577323024</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9235948343007974</v>
+        <v>-0.8694192247404113</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.716014221602073</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.53718697590419</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12717775845472</v>
+        <v>-9.991738734553753</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8847323338036621</v>
+        <v>-0.8305567242432761</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.648028471741516</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.577678110847063</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10322421747876</v>
+        <v>-9.967785193577795</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8744824112677851</v>
+        <v>-0.8203068017073991</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.624074930765559</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.592718741578131</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.839164279155963</v>
+        <v>-9.703725255254998</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7821187521004185</v>
+        <v>-0.7279431425400325</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.360014992442763</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.737894388410057</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.132084655651125</v>
+        <v>-9.17137995022596</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5020739363587845</v>
+        <v>-0.5177920541887184</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.360014992442763</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.735107354749756</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.091900357284935</v>
+        <v>-9.13119565185977</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.485656593124467</v>
+        <v>-0.5013747109544009</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.319830694076572</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.759561557657312</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.01183056174713</v>
+        <v>-9.051125856321965</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4542618536885881</v>
+        <v>-0.469979971518522</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.239760898538768</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.806970256200751</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.778349339517533</v>
+        <v>-8.817644634092368</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3529449359588965</v>
+        <v>-0.3686630537888305</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.006279676309169</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.954983418376362</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.628682948510018</v>
+        <v>-8.667978243084853</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2959705898688503</v>
+        <v>-0.3116887076987842</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-1.913376185066633</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>2.007833302808925</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.496407474879131</v>
+        <v>-8.535702769453966</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2476929136694683</v>
+        <v>-0.2634110314994023</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.781100711435747</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.082566073734484</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.305807800205978</v>
+        <v>-8.345103094780812</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1686379831125699</v>
+        <v>-0.1843561009425039</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.590501036762594</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.199740939226012</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.056808001522397</v>
+        <v>-8.096103296097231</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.0561317224154787</v>
+        <v>-0.07184984024541263</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.590501036762594</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.212647280449671</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.162397991295501</v>
+        <v>-8.201693285870336</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2263436479239394</v>
+        <v>-0.2420617657538733</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.696091026535698</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>2.02131735698659</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.181132893414098</v>
+        <v>-8.220428187988933</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1852932668942917</v>
+        <v>-0.2010113847242256</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.701687036195829</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.066504093067597</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.033192852006499</v>
+        <v>-8.072488146581334</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2459961730194196</v>
+        <v>-0.2617142908493535</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.681366120287272</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.958817719924564</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.016034701875205</v>
+        <v>-8.055329996450039</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2478468992203799</v>
+        <v>-0.2635650170503139</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.664207970155978</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.960398623749863</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.972486295104514</v>
+        <v>-8.011781589679348</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2373881486071969</v>
+        <v>-0.2531062664371309</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.664207970155978</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.95343801165477</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.730337901650656</v>
+        <v>-7.76963319622549</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1260664368445106</v>
+        <v>-0.1417845546744445</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.664207970155978</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.967900366035913</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.622078764528134</v>
+        <v>-7.661374059102968</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08823066153630688</v>
+        <v>-0.1039487793662408</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.664207970155978</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.962432486495108</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.498787629711003</v>
+        <v>-7.538082924285837</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04141611359887776</v>
+        <v>-0.05713423142881124</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.540916835338847</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.033905261395963</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.47763843080756</v>
+        <v>-7.516933725382394</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02525545580017541</v>
+        <v>-0.04097357363010889</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.519767636435404</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.054295758975354</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.233872988824116</v>
+        <v>-7.27316828339895</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06803142934025308</v>
+        <v>0.05231331151031959</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.519767636435404</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.050076467322405</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.132110168546821</v>
+        <v>-7.171405463121655</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1108608713711869</v>
+        <v>0.09514275354125346</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.506548568042975</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.060132222277878</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.882259774597746</v>
+        <v>-6.92155506917258</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.203543103934519</v>
+        <v>0.1878249861045855</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.506548568042975</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.05287429726158</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.706367682130313</v>
+        <v>-6.745662976705148</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2774990644421411</v>
+        <v>0.2617809466122072</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.506548568042975</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.056473420782229</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.53492121910785</v>
+        <v>-6.574216513682685</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3594051557056801</v>
+        <v>0.3436870378757462</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.335102105020512</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.17266880465026</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.309888219439027</v>
+        <v>-6.349183514013862</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4484388331895062</v>
+        <v>0.4327207153595722</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.110069105351689</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.306709082067851</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.246252477205092</v>
+        <v>-6.285547771779927</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4785879311373971</v>
+        <v>0.4628698133074631</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.046433363117754</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.349585328462529</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.202490295899251</v>
+        <v>-6.241785590474086</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4772870624435295</v>
+        <v>0.4615689446135955</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.046433363117754</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.330779587246325</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.962059799094391</v>
+        <v>-6.001355093669225</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5752023377903512</v>
+        <v>0.5594842199604173</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8060028663128942</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.476780961954118</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.889817230923196</v>
+        <v>-5.929112525498031</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6080286788936493</v>
+        <v>0.5923105610637154</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8060028663128942</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.480710275788939</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.836818908641808</v>
+        <v>-5.876114203216643</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6299065917235445</v>
+        <v>0.6141884738936105</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7506666073109554</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.514590615107442</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.728014023162081</v>
+        <v>-5.767309317736916</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6704266171354285</v>
+        <v>0.6547084993054946</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7506666073109554</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.511588686327435</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.507993225125071</v>
+        <v>-5.547288519699905</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7600139733608469</v>
+        <v>0.7442958555309129</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6094467622429751</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.597899630378838</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.375125536061793</v>
+        <v>-5.414420830636628</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8290552317879811</v>
+        <v>0.8133371139580472</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6094467622429751</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.613793813180661</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.215610432542423</v>
+        <v>-5.254905727117258</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8940071176360309</v>
+        <v>0.878288999806097</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.4499316587236052</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.710648719732585</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.070938287442686</v>
+        <v>-5.11023358201752</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.961964078237366</v>
+        <v>0.946245960407432</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.3052595136238678</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.807540109353867</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.130813114800378</v>
+        <v>-5.170108409375213</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9240516386957149</v>
+        <v>0.908333520865781</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3651343409815599</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.757652704340678</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.044013617021369</v>
+        <v>-5.083308911596204</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9811719311298845</v>
+        <v>0.9654538132999506</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3651343409815599</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.780053197663244</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.046483323483175</v>
+        <v>-5.08577861805801</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9802564499185742</v>
+        <v>0.9645383320886403</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.3676040474433661</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.778643775159572</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.114853509807185</v>
+        <v>-5.15414880438202</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9639152978636725</v>
+        <v>0.9481971800337385</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3583283484071511</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.795216117056003</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.223391690723319</v>
+        <v>-5.262686985298154</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9109367341291099</v>
+        <v>0.895218616299176</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3583283484071511</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.785652825687894</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.254384850052024</v>
+        <v>-5.293680144626859</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7232490354380148</v>
+        <v>0.7075309176080808</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3583283484071511</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.610362390728281</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.078910590259555</v>
+        <v>-5.11820588483439</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.79800597134679</v>
+        <v>0.782287853516856</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3583283484071511</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.614929622720069</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.091490523822313</v>
+        <v>-5.229142137475639</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7687160266828941</v>
+        <v>0.7136553812215634</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3583283484071511</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.590671651481276</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.294517101365546</v>
+        <v>-5.432168715018872</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6906367808855065</v>
+        <v>0.6355761354241758</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5613549259503845</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.471987090175241</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.136591502430253</v>
+        <v>-5.274243116083579</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7639794068917558</v>
+        <v>0.7089187614304255</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5613549259503845</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.482159476607374</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.050348039403875</v>
+        <v>-5.187999653057202</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7934230626761671</v>
+        <v>0.7383624172148369</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5613549259503845</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.477105747181234</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.095654858802855</v>
+        <v>-5.233306472456182</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.767076110361101</v>
+        <v>0.7120154648997703</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6021650889596153</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.444395424820221</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.124687963505156</v>
+        <v>-5.262339577158483</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7560147415132819</v>
+        <v>0.7009540960519516</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6021650889596153</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.444947297853323</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.031877482054297</v>
+        <v>-5.169529095707623</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7224116259849915</v>
+        <v>0.6673509805236608</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.5093546075087559</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.429906278615204</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.076266951383724</v>
+        <v>-5.213918565037051</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7065293141778213</v>
+        <v>0.651468668716491</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.5537440768381836</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.405146072942149</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.963595733147474</v>
+        <v>-5.1012473468008</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7466735099840445</v>
+        <v>0.691612864522714</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4410728586019334</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.467824512395622</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.851218731964801</v>
+        <v>-4.988870345618127</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7971156062877809</v>
+        <v>0.7420549608264504</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4410728586019334</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.473315808226289</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.049453300851532</v>
+        <v>-5.187104914504858</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7293189805016276</v>
+        <v>0.6742583350402969</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.639307427488664</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.365872268662789</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.132454581876811</v>
+        <v>-5.270106195530137</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5344741880921693</v>
+        <v>0.4794135426308386</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6578783120158378</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.193085457947138</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.241068660320142</v>
+        <v>-5.378720273973468</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6111782174340425</v>
+        <v>0.5561175719727118</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6578783120158378</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.313235118666344</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.327667243301245</v>
+        <v>-5.465318856954571</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5910518103439242</v>
+        <v>0.5359911648825939</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6578783120158378</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.327748144768667</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.289283580743094</v>
+        <v>-5.42693519439642</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6038247167095534</v>
+        <v>0.5487640712482227</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6194946494576866</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.348197783645927</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.112167250707928</v>
+        <v>-5.249818864361254</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6714002775689218</v>
+        <v>0.6163396321075911</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6194946494576866</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.344926812491229</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.157259495541473</v>
+        <v>-5.2949111091948</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6540467713974167</v>
+        <v>0.598986125936086</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7757132599384265</v>
+        <v>-0.6813906926270764</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.251879037964698</v>
+        <v>2.308472578351508</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.977884074302706</v>
+        <v>-5.115535687956032</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.719583915199338</v>
+        <v>0.6645232697380075</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6189365017677079</v>
+        <v>-0.5246139344563577</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339732068173543</v>
+        <v>2.396325608560353</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.022898287823311</v>
+        <v>-5.160549901476639</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6823856851226853</v>
+        <v>0.6273250396613546</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6492853970823125</v>
+        <v>-0.5549628297709623</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.30233018631637</v>
+        <v>2.35892372670318</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.289902798095746</v>
+        <v>-5.427554411749074</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.581275443352657</v>
+        <v>0.5262147978913263</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-0.749325867813911</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.247997466216357</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.391100579532919</v>
+        <v>-5.528752193186246</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5400002526742895</v>
+        <v>0.4849396072129588</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.8177346813592301</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.206156099985667</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.358624993362147</v>
+        <v>-5.496276607015474</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5505904486969153</v>
+        <v>0.4955298032355842</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.8177346813592301</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.203756061539984</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.33958686565485</v>
+        <v>-5.477238479308177</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5547304189880791</v>
+        <v>0.4996697735267479</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.8759182926904246</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>2.165370613949512</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.370713496805468</v>
+        <v>-5.508365110458795</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7198616354665122</v>
+        <v>0.6648009900051814</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.8759182926904246</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.342952482888192</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.42303387740626</v>
+        <v>-5.560685491059587</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6997668122123288</v>
+        <v>0.6447061667509981</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.8409714326815525</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.364753927879649</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.443291175935218</v>
+        <v>-5.580942789588545</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6976724231976719</v>
+        <v>0.6426117777363407</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.8409714326815525</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.370762458276575</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.295548205700215</v>
+        <v>-5.433199819353542</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8359222590836946</v>
+        <v>0.7808616136223638</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.6731640754466693</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.550599520409527</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.397562888231437</v>
+        <v>-5.535214501884764</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7979100076026873</v>
+        <v>0.7428493621413561</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.6731640754466693</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.553393141941008</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.260953544137344</v>
+        <v>-5.398605157790671</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8532160936319828</v>
+        <v>0.7981554481706516</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6308772986639271</v>
+        <v>-0.5365547313525769</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.579427556402312</v>
+        <v>2.636021096789122</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.403718876959994</v>
+        <v>-5.541370490613321</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7951904372430327</v>
+        <v>0.740129791781702</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.6793200641752273</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.492848833448832</v>
+        <v>2.549442373835642</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.341420878183872</v>
+        <v>-5.479072491837199</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8864451905503028</v>
+        <v>0.8313845450889716</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.6793200641752273</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.559184387245653</v>
+        <v>2.615777927632462</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.139630680518714</v>
+        <v>-5.277282294172041</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6757421420057637</v>
+        <v>0.6206814965444329</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.575624439317423</v>
+        <v>-0.4813018720060729</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.386576174936543</v>
+        <v>2.443169715323353</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.07973999887612</v>
+        <v>-5.217391612529448</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7699886469849764</v>
+        <v>0.7149280015236457</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5157337576748295</v>
+        <v>-0.4214111903634794</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.492800816244275</v>
+        <v>2.549394356631085</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.177480543501095</v>
+        <v>-5.315132157154422</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7455201652510302</v>
+        <v>0.6904595197896994</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5316230358078098</v>
+        <v>-0.4373004684964596</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.49789498548053</v>
+        <v>2.55448852586734</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.353818303624024</v>
+        <v>-5.491469917277351</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6735210420265303</v>
+        <v>0.6184603965651991</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.613638228619389</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.390628310231444</v>
+        <v>2.447221850618254</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.353128931462801</v>
+        <v>-5.490780545116128</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6722884089309482</v>
+        <v>0.6172277634696171</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.613638228619389</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.389119928271373</v>
+        <v>2.445713468658183</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.359699896517394</v>
+        <v>-5.497351510170721</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6695228903445472</v>
+        <v>0.6144622448832164</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.620209193673982</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.385040216674053</v>
+        <v>2.441633757060863</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.351745926222621</v>
+        <v>-5.489397539875949</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6727044784624558</v>
+        <v>0.6176438330011251</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.620209193673982</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.385040216674053</v>
+        <v>2.441633757060863</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.341372549889535</v>
+        <v>-5.479024163542862</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6832355860234953</v>
+        <v>0.6281749405621646</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7041583846522448</v>
+        <v>-0.6098358173408946</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.39764599950171</v>
+        <v>2.45423953988852</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.213688240095238</v>
+        <v>-5.351339853748565</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7392016833159389</v>
+        <v>0.6841410378546078</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5764740748579483</v>
+        <v>-0.4821515075465982</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.479148958753013</v>
+        <v>2.535742499139823</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.274354830497627</v>
+        <v>-5.412006444150954</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7016897196308554</v>
+        <v>0.6466290741695246</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.658172391576482</v>
+        <v>-0.5638498242651319</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.416884641197765</v>
+        <v>2.473478181584575</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.209360970563981</v>
+        <v>-5.347012584217309</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7317849662149425</v>
+        <v>0.6767243207536113</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6313417769723266</v>
+        <v>-0.5370192096609765</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.437080712570887</v>
+        <v>2.493674252957697</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.310119606320979</v>
+        <v>-5.447771219974307</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6956424515432209</v>
+        <v>0.6405818060818902</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7201673456993321</v>
+        <v>-0.6258447783879819</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.387946310965761</v>
+        <v>2.444539851352571</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.265916769235079</v>
+        <v>-5.403568382888406</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7192031889054182</v>
+        <v>0.6641425434440875</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6759645086134316</v>
+        <v>-0.5816419413020815</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.420347615745139</v>
+        <v>2.476941156131949</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.302895796898522</v>
+        <v>-5.440547410551849</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.702821578309289</v>
+        <v>0.6477609328479579</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.5446680395107509</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.440941957289184</v>
+        <v>2.497535497675995</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.322953875763362</v>
+        <v>-5.46060548941669</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7460461119463924</v>
+        <v>0.6909854664850612</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.5446680395107509</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.492189722472224</v>
+        <v>2.548783262859034</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.283023202585472</v>
+        <v>-5.420674816238799</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7604590858118017</v>
+        <v>0.7053984403504705</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5990599336442107</v>
+        <v>-0.5047373663328606</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.514588830973212</v>
+        <v>2.571182371360022</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.242552855022767</v>
+        <v>-5.380204468676094</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7715954530751534</v>
+        <v>0.7165348076138227</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5585895860815058</v>
+        <v>-0.4642670187701556</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.533819267749104</v>
+        <v>2.590412808135914</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.177328673895562</v>
+        <v>-5.314980287548889</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8148725296187407</v>
+        <v>0.7598118841574095</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.39904283764295</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590141180518133</v>
+        <v>2.646734720904943</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.494849985589694</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.227822964252618</v>
+        <v>-5.365474577905945</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7906357857751987</v>
+        <v>0.7355751403138675</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.5383861420803744</v>
+        <v>-0.4440635747690242</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.559089710541769</v>
+        <v>2.615683250928579</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>4.01743599277118</v>
+        <v>3.841548506867616</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.890144269074951</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.227822964252618</v>
+        <v>-5.459323449846447</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7906357857751987</v>
+        <v>0.6992923838689071</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.5383861420803744</v>
+        <v>-0.4421016629853325</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.883208066061319</v>
+        <v>2.618117190330034</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240609.xlsx
+++ b/tame_output/ON/bt/strategyON_20240609.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.3%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-707.5%</t>
+          <t>-689.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-306.3%</t>
+          <t>-297.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.5%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.2%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.2%</t>
+          <t>-188.8%</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.460765905223921</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2675006315807229</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.598833449148414</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.157862085333545</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.665797085998237</v>
+        <v>-8.757902275471551</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3535394084248527</v>
+        <v>-0.3903814842141777</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.598833449148414</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.153835780799142</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.048798474740869</v>
+        <v>-9.140903664214182</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5068420652434891</v>
+        <v>-0.5436841410328146</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.598833449148414</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.153733679477558</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.230668265725903</v>
+        <v>-9.322773455199217</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5770184656660726</v>
+        <v>-0.6138605414553981</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.780703240133449</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.047183320857967</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.590198588229905</v>
+        <v>-9.682303777703218</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.715480291369623</v>
+        <v>-0.7523223671589485</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.780703240133449</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.052533624156017</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.640547651684127</v>
+        <v>-9.73265284115744</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7277038967941345</v>
+        <v>-0.76454597258346</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.831052303587671</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.030240206040661</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.738166929105523</v>
+        <v>-9.830272118578836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.763709857140924</v>
+        <v>-0.8005519329302495</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.928671581009067</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.974710390209593</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.885693017111166</v>
+        <v>-9.977798206584479</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8198267360216089</v>
+        <v>-0.8566688118109345</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.076197669014711</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.889088293727778</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.08995119244103</v>
+        <v>-10.18205638191434</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8960168090349123</v>
+        <v>-0.9328588848242374</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.2038366136287</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.818018124078028</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23176096664782</v>
+        <v>-10.32386615612113</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9482581642331911</v>
+        <v>-0.9851002400225171</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.375115411274275</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.719733399975118</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.15829113498037</v>
+        <v>-10.25039632445368</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9034985300727909</v>
+        <v>-0.940340605862116</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.301645579606827</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.779187000469008</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33341555236691</v>
+        <v>-10.42552074184023</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9589930762798913</v>
+        <v>-0.9958351520692164</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.476769996993371</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.688667570784599</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.5678676463814</v>
+        <v>-10.65997283585472</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.059993078787283</v>
+        <v>-1.096835154576608</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.476769996993371</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.681448405883003</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85567149091864</v>
+        <v>-10.94777668039195</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.181786807376155</v>
+        <v>-1.21862888316548</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.764573841530609</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.502093908386684</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.90845764651897</v>
+        <v>-11.00056283599228</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.201785479777729</v>
+        <v>-1.238627555567055</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.860249328113006</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.445804406275802</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03449443988726</v>
+        <v>-11.12659962936057</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.24950646849593</v>
+        <v>-1.286348544285256</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.834997705303263</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.463649108590762</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98247892591844</v>
+        <v>-11.07458411539176</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.224709927222004</v>
+        <v>-1.261552003011329</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.834997705303263</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.467639444277163</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.12415076764256</v>
+        <v>-11.21625595711588</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.282853890810394</v>
+        <v>-1.319695966599719</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.834997705303263</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.466164217378421</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.07455992321773</v>
+        <v>-11.16666511269104</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.247964142875588</v>
+        <v>-1.284806218664913</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.785406860878429</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.510972134198194</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.06175253021295</v>
+        <v>-11.15385771968627</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.255892319320361</v>
+        <v>-1.292734395109686</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.834262635887331</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.46860753554617</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.83590737749354</v>
+        <v>-10.92801256696686</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.155975185196388</v>
+        <v>-1.192817260985713</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.792335960300167</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.503342613934677</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.71132872115595</v>
+        <v>-10.80343391062926</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.105004578105293</v>
+        <v>-1.141846653894617</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.792335960300167</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.504481758490736</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.76422400920024</v>
+        <v>-10.85632919867355</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.1235289191609</v>
+        <v>-1.160370994950225</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.787380614211721</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.510088740305911</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69209083391236</v>
+        <v>-10.78419602338567</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.088941944807111</v>
+        <v>-1.125784020596435</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.787380614211721</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.515822444544548</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62072444130271</v>
+        <v>-10.71282963077602</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.070132650157117</v>
+        <v>-1.106974725946442</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.716014221602073</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.548905017716471</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.35688757409864</v>
+        <v>-10.44899276357195</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9744813845883971</v>
+        <v>-1.011323460377721</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.716014221602073</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.539021536403564</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.08964577323024</v>
+        <v>-10.18175096270356</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8694192247404113</v>
+        <v>-0.9062613005297364</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.716014221602073</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.53718697590419</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.991738734553753</v>
+        <v>-10.08384392402706</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8305567242432761</v>
+        <v>-0.8673988000326003</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.648028471741516</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.577678110847063</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.967785193577795</v>
+        <v>-10.05989038305111</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8203068017073991</v>
+        <v>-0.8571488774967242</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.624074930765559</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.592718741578131</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.703725255254998</v>
+        <v>-9.79583044472831</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7279431425400325</v>
+        <v>-0.7647852183293571</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.360014992442763</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.737894388410057</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.17137995022596</v>
+        <v>-9.088750821223472</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5177920541887184</v>
+        <v>-0.4847404025877231</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.360014992442763</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.735107354749756</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.13119565185977</v>
+        <v>-9.048566522857282</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5013747109544009</v>
+        <v>-0.4683230593534056</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.319830694076572</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.759561557657312</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.051125856321965</v>
+        <v>-8.968496727319478</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.469979971518522</v>
+        <v>-0.4369283199175271</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.239760898538768</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.806970256200751</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.817644634092368</v>
+        <v>-8.73501550508988</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3686630537888305</v>
+        <v>-0.3356114021878356</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.006279676309169</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.954983418376362</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.667978243084853</v>
+        <v>-8.585349114082366</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3116887076987842</v>
+        <v>-0.2786370560977889</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.913376185066633</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.007833302808925</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.535702769453966</v>
+        <v>-8.453073640451478</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2634110314994023</v>
+        <v>-0.2303593798984069</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.781100711435747</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.082566073734484</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.345103094780812</v>
+        <v>-8.262473965778325</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1843561009425039</v>
+        <v>-0.151304449341509</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.590501036762594</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.199740939226012</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.096103296097231</v>
+        <v>-8.013474167094744</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.07184984024541263</v>
+        <v>-0.03879818864441775</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.590501036762594</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.212647280449671</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.201693285870336</v>
+        <v>-8.119064156867848</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2420617657538733</v>
+        <v>-0.2090101141528784</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.696091026535698</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.02131735698659</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.220428187988933</v>
+        <v>-8.137799058986445</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2010113847242256</v>
+        <v>-0.1679597331232308</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.701687036195829</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.066504093067597</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.072488146581334</v>
+        <v>-7.989859017578846</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2617142908493535</v>
+        <v>-0.2286626392483586</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.681366120287272</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.958817719924564</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.055329996450039</v>
+        <v>-7.972700867447552</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2635650170503139</v>
+        <v>-0.230513365449319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.664207970155978</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.960398623749863</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.011781589679348</v>
+        <v>-7.929152460676861</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2531062664371309</v>
+        <v>-0.220054614836136</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.664207970155978</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.95343801165477</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.76963319622549</v>
+        <v>-7.687004067223003</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1417845546744445</v>
+        <v>-0.1087329030734496</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.664207970155978</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.967900366035913</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.661374059102968</v>
+        <v>-7.578744930100481</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1039487793662408</v>
+        <v>-0.07089712776524593</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.664207970155978</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.962432486495108</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.538082924285837</v>
+        <v>-7.455453795283351</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05713423142881124</v>
+        <v>-0.02408257982781681</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.540916835338847</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.033905261395963</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.516933725382394</v>
+        <v>-7.434304596379907</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.04097357363010889</v>
+        <v>-0.007921922029114015</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.519767636435404</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.054295758975354</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.27316828339895</v>
+        <v>-7.190539154396463</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05231331151031959</v>
+        <v>0.08536496311131403</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.519767636435404</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.050076467322405</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.171405463121655</v>
+        <v>-7.088776334119168</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09514275354125346</v>
+        <v>0.1281944051422483</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.506548568042975</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.060132222277878</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.92155506917258</v>
+        <v>-6.838925940170093</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1878249861045855</v>
+        <v>0.22087663770558</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.506548568042975</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.05287429726158</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.745662976705148</v>
+        <v>-6.66303384770266</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2617809466122072</v>
+        <v>0.2948325982132021</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.506548568042975</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.056473420782229</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.574216513682685</v>
+        <v>-6.491587384680197</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3436870378757462</v>
+        <v>0.3767386894767411</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.335102105020512</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.17266880465026</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.349183514013862</v>
+        <v>-6.266554385011374</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4327207153595722</v>
+        <v>0.4657723669605671</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.110069105351689</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.306709082067851</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.285547771779927</v>
+        <v>-6.20291864277744</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4628698133074631</v>
+        <v>0.4959214649084585</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.046433363117754</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.349585328462529</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.241785590474086</v>
+        <v>-6.159156461471598</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4615689446135955</v>
+        <v>0.4946205962145904</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.046433363117754</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.330779587246325</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.001355093669225</v>
+        <v>-5.918725964666738</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5594842199604173</v>
+        <v>0.5925358715614122</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8060028663128942</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.476780961954118</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.929112525498031</v>
+        <v>-5.846483396495543</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5923105610637154</v>
+        <v>0.6253622126647103</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8060028663128942</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.480710275788939</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.876114203216643</v>
+        <v>-5.793485074214155</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6141884738936105</v>
+        <v>0.6472401254946054</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7506666073109554</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.514590615107442</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.767309317736916</v>
+        <v>-5.675688727528015</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6547084993054946</v>
+        <v>0.6913567353890553</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7506666073109554</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.511588686327435</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.547288519699905</v>
+        <v>-5.455667929491004</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7442958555309129</v>
+        <v>0.7809440916144736</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6094467622429751</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.597899630378838</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.414420830636628</v>
+        <v>-5.322800240427727</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8133371139580472</v>
+        <v>0.8499853500416079</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6094467622429751</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.613793813180661</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.254905727117258</v>
+        <v>-5.163285136908357</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.878288999806097</v>
+        <v>0.9149372358896577</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4499316587236052</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.710648719732585</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.11023358201752</v>
+        <v>-5.018612991808619</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.946245960407432</v>
+        <v>0.9828941964909923</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3052595136238678</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.807540109353867</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.170108409375213</v>
+        <v>-5.078487819166312</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.908333520865781</v>
+        <v>0.9449817569493413</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3651343409815599</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.757652704340678</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.083308911596204</v>
+        <v>-4.991688321387302</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9654538132999506</v>
+        <v>1.002102049383511</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3651343409815599</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.780053197663244</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.08577861805801</v>
+        <v>-4.994158027849108</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9645383320886403</v>
+        <v>1.001186568172201</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3676040474433661</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.778643775159572</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.15414880438202</v>
+        <v>-5.062528214173119</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9481971800337385</v>
+        <v>0.9848454161172988</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3583283484071511</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.795216117056003</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.262686985298154</v>
+        <v>-5.171066395089253</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.895218616299176</v>
+        <v>0.9318668523827367</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3583283484071511</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.785652825687894</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.293680144626859</v>
+        <v>-5.202059554417958</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7075309176080808</v>
+        <v>0.7441791536916411</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3583283484071511</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.610362390728281</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.11820588483439</v>
+        <v>-5.026585294625489</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.782287853516856</v>
+        <v>0.8189360896004163</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3583283484071511</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.614929622720069</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.229142137475639</v>
+        <v>-5.137521547266738</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7136553812215634</v>
+        <v>0.7503036173051241</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3583283484071511</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.590671651481276</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.432168715018872</v>
+        <v>-5.340548124809971</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6355761354241758</v>
+        <v>0.6722243715077361</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5613549259503845</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.471987090175241</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.274243116083579</v>
+        <v>-5.182622525874678</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7089187614304255</v>
+        <v>0.7455669975139858</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5613549259503845</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.482159476607374</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.187999653057202</v>
+        <v>-5.096379062848301</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7383624172148369</v>
+        <v>0.7750106532983971</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5613549259503845</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.477105747181234</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.233306472456182</v>
+        <v>-5.14168588224728</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7120154648997703</v>
+        <v>0.748663700983331</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6021650889596153</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.444395424820221</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.262339577158483</v>
+        <v>-5.170718986949582</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7009540960519516</v>
+        <v>0.7376023321355119</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6021650889596153</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.444947297853323</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.169529095707623</v>
+        <v>-5.077908505498722</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6673509805236608</v>
+        <v>0.7039992166072215</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5093546075087559</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.429906278615204</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.213918565037051</v>
+        <v>-5.122297974828149</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.651468668716491</v>
+        <v>0.6881169048000513</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5537440768381836</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.405146072942149</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.1012473468008</v>
+        <v>-5.009626756591899</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.691612864522714</v>
+        <v>0.7282611006062742</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4410728586019334</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.467824512395622</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.988870345618127</v>
+        <v>-4.897249755409226</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7420549608264504</v>
+        <v>0.7787031969100107</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4410728586019334</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.473315808226289</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.187104914504858</v>
+        <v>-5.095484324295957</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6742583350402969</v>
+        <v>0.7109065711238576</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.639307427488664</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.365872268662789</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.270106195530137</v>
+        <v>-5.178485605321236</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4794135426308386</v>
+        <v>0.5160617787143993</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6578783120158378</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.193085457947138</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.378720273973468</v>
+        <v>-5.287099683764567</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5561175719727118</v>
+        <v>0.5927658080562725</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6578783120158378</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.313235118666344</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.465318856954571</v>
+        <v>-5.37369826674567</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5359911648825939</v>
+        <v>0.5726394009661542</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6578783120158378</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.327748144768667</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.42693519439642</v>
+        <v>-5.335314604187519</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5487640712482227</v>
+        <v>0.5854123073317834</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6194946494576866</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.348197783645927</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.249818864361254</v>
+        <v>-5.158198274152353</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6163396321075911</v>
+        <v>0.6529878681911518</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6194946494576866</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.344926812491229</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.2949111091948</v>
+        <v>-5.203290518985899</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.598986125936086</v>
+        <v>0.6356343620196463</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6813906926270764</v>
+        <v>-0.7757132599384265</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.308472578351508</v>
+        <v>2.251879037964698</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.115535687956032</v>
+        <v>-5.023915097747131</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6645232697380075</v>
+        <v>0.7011715058215677</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5246139344563577</v>
+        <v>-0.6189365017677079</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.396325608560353</v>
+        <v>2.339732068173543</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.160549901476639</v>
+        <v>-5.068929311267738</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6273250396613546</v>
+        <v>0.6639732757449148</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5549628297709623</v>
+        <v>-0.6492853970823125</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.35892372670318</v>
+        <v>2.30233018631637</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.427554411749074</v>
+        <v>-5.335933821540173</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5262147978913263</v>
+        <v>0.5628630339748866</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.749325867813911</v>
+        <v>-0.8436484351252611</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.247997466216357</v>
+        <v>2.191403925829547</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.528752193186246</v>
+        <v>-5.437131602977345</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4849396072129588</v>
+        <v>0.5215878432965191</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8177346813592301</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.206156099985667</v>
+        <v>2.149562559598857</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.496276607015474</v>
+        <v>-5.404656016806573</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4955298032355842</v>
+        <v>0.5321780393191449</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8177346813592301</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.203756061539984</v>
+        <v>2.147162521153174</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.477238479308177</v>
+        <v>-5.385617889099276</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4996697735267479</v>
+        <v>0.5363180096103086</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8759182926904246</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.165370613949512</v>
+        <v>2.108777073562702</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.508365110458795</v>
+        <v>-5.416744520249894</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6648009900051814</v>
+        <v>0.7014492260887417</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8759182926904246</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.342952482888192</v>
+        <v>2.286358942501382</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.560685491059587</v>
+        <v>-5.469064900850686</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6447061667509981</v>
+        <v>0.6813544028345584</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.8409714326815525</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.364753927879649</v>
+        <v>2.308160387492839</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.580942789588545</v>
+        <v>-5.489322199379644</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6426117777363407</v>
+        <v>0.6792600138199014</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.8409714326815525</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.370762458276575</v>
+        <v>2.314168917889765</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.433199819353542</v>
+        <v>-5.341579229144641</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7808616136223638</v>
+        <v>0.8175098497059241</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.6731640754466693</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.550599520409527</v>
+        <v>2.494005980022717</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.535214501884764</v>
+        <v>-5.443593911675863</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7428493621413561</v>
+        <v>0.7794975982249168</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.6731640754466693</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.553393141941008</v>
+        <v>2.496799601554198</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.019812048044207</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.398605157790671</v>
+        <v>-5.30698456758177</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7981554481706516</v>
+        <v>0.8966617966977521</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5365547313525769</v>
+        <v>-0.6308772986639271</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.636021096789122</v>
+        <v>2.641285668845851</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.018892524784317</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.541370490613321</v>
+        <v>-5.44974990040442</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.740129791781702</v>
+        <v>0.8386361403088021</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6793200641752273</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.549442373835642</v>
+        <v>2.554706945892371</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.085228078581138</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.479072491837199</v>
+        <v>-5.387451901628298</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8313845450889716</v>
+        <v>0.9298908936160721</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6793200641752273</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.615777927632462</v>
+        <v>2.621042499689192</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.793808950970536</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.277282294172041</v>
+        <v>-5.18566170396314</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6206814965444329</v>
+        <v>0.719187845071533</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4813018720060729</v>
+        <v>-0.575624439317423</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.443169715323353</v>
+        <v>2.448434287380083</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.864099183292712</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.217391612529448</v>
+        <v>-5.125771022320547</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7149280015236457</v>
+        <v>0.8134343500507457</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4214111903634794</v>
+        <v>-0.5157337576748295</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.549394356631085</v>
+        <v>2.554658928687815</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.878726919408755</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.315132157154422</v>
+        <v>-5.223511566945521</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6904595197896994</v>
+        <v>0.7889658683167995</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4373004684964596</v>
+        <v>-0.5316230358078098</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.55448852586734</v>
+        <v>2.55975309792407</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.877262900233427</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.491469917277351</v>
+        <v>-5.39984932706845</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6184603965651991</v>
+        <v>0.7169667450922996</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.613638228619389</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.447221850618254</v>
+        <v>2.452486422674984</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.875754518273355</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.490780545116128</v>
+        <v>-5.399159954907227</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6172277634696171</v>
+        <v>0.7157341119967175</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.613638228619389</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.445713468658183</v>
+        <v>2.450978040714912</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875617385708792</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.497351510170721</v>
+        <v>-5.40573091996182</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6144622448832164</v>
+        <v>0.7129685934103165</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.620209193673982</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.441633757060863</v>
+        <v>2.446898329117593</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875617385708792</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.489397539875949</v>
+        <v>-5.397776949667048</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6176438330011251</v>
+        <v>0.7161501815282252</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.620209193673982</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.441633757060863</v>
+        <v>2.446898329117593</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.881999142736596</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.479024163542862</v>
+        <v>-5.387403573333961</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6281749405621646</v>
+        <v>0.7266812890892647</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6098358173408946</v>
+        <v>-0.7041583846522448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.45423953988852</v>
+        <v>2.45950411194525</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.886891516111321</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.351339853748565</v>
+        <v>-5.259719263539664</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6841410378546078</v>
+        <v>0.7826473863817083</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4821515075465982</v>
+        <v>-0.5764740748579483</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.535742499139823</v>
+        <v>2.541007071196553</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.873646188587193</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.412006444150954</v>
+        <v>-5.320385853942053</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6466290741695246</v>
+        <v>0.7451354226966247</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5638498242651319</v>
+        <v>-0.658172391576482</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.473478181584575</v>
+        <v>2.478742753641304</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.877743891197822</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.347012584217309</v>
+        <v>-5.255391994008408</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6767243207536113</v>
+        <v>0.7752306692807118</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.5370192096609765</v>
+        <v>-0.6313417769723266</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.493674252957697</v>
+        <v>2.498938825014426</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.8819048308289</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.447771219974307</v>
+        <v>-5.356150629765406</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6405818060818902</v>
+        <v>0.7390881546089902</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6258447783879819</v>
+        <v>-0.7201673456993321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.444539851352571</v>
+        <v>2.449804423409301</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.887784433356737</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.403568382888406</v>
+        <v>-5.311947792679505</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6641425434440875</v>
+        <v>0.7626488919711876</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5816419413020815</v>
+        <v>-0.6759645086134316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.476941156131949</v>
+        <v>2.482205728188679</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.886194433825985</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.440547410551849</v>
+        <v>-5.348926820342948</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6477609328479579</v>
+        <v>0.7462672813750584</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5446680395107509</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.497535497675995</v>
+        <v>2.502800069732724</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.937442199009024</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.46060548941669</v>
+        <v>-5.368984899207788</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6909854664850612</v>
+        <v>0.7894918150121617</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5446680395107509</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.548783262859034</v>
+        <v>2.554047834915764</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.935882903603277</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.420674816238799</v>
+        <v>-5.329054226029898</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7053984403504705</v>
+        <v>0.803904788877571</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5047373663328606</v>
+        <v>-0.5990599336442107</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.571182371360022</v>
+        <v>2.576446943416752</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.930831131841547</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.380204468676094</v>
+        <v>-5.288583878467193</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7165348076138227</v>
+        <v>0.8150411561409228</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4642670187701556</v>
+        <v>-0.5585895860815058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.590412808135914</v>
+        <v>2.595677380192644</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.948018535934252</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.314980287548889</v>
+        <v>-5.223359697339988</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7598118841574095</v>
+        <v>0.85831823268451</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.39904283764295</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.646734720904943</v>
+        <v>2.651999292961673</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.943979508233533</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.365474577905945</v>
+        <v>-5.273853987697044</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7355751403138675</v>
+        <v>0.834081488840968</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4440635747690242</v>
+        <v>-0.5383861420803744</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.615683250928579</v>
+        <v>2.620947822985308</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.841548506867616</v>
+        <v>3.806014114269817</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.89510073265448</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.459323449846447</v>
+        <v>-5.276006494317704</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.6992923838689071</v>
+        <v>0.784341710613651</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.4421016629853325</v>
+        <v>-0.5383861420803744</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.618117190330034</v>
+        <v>2.572069047406256</v>
       </c>
     </row>
   </sheetData>
